--- a/aqt_docs.xlsx
+++ b/aqt_docs.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28380" windowHeight="11325" firstSheet="2" activeTab="10"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28380" windowHeight="11325" firstSheet="3" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="사용법" sheetId="4" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="기타환경변수" sheetId="3" r:id="rId9"/>
     <sheet name="Sheet1" sheetId="9" r:id="rId10"/>
     <sheet name="Sheet3" sheetId="11" r:id="rId11"/>
+    <sheet name="Sheet2" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="492">
   <si>
     <t>tapphosts</t>
   </si>
@@ -2445,41 +2446,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Prog No</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수행구분</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>소스구분</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>프로그램명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>개별송신전</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>JS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>사용자명변경</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 테스트 시작 전 
-2.개별송신전 
-3.개별송신후  
-4.테스트 완료후</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">    dstf: </t>
     </r>
@@ -2839,12 +2805,196 @@
     <t>테스트 대상 서비스 확정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>업무구분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로그램명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신규/변경일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미사용구분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>컴파일/빌드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전환(U2L)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기능테스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>거래코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서비스id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수신</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>svc001.c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>svc001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TR001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TR002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TR003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TR004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>com001.c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>svc010.c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미사용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수작업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수작업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수작업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수작업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>svc010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로그</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로그</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로그</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트원본</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>담당자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>홍길동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김갑돌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이수일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빌드파일명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>svr01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>libcomx.so</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>svr10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>계좌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>svc099.c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김중배</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>svc009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>svr99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TR050</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수작업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TR010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>U2L 전환 및 테스트 현황</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="46" x14ac:knownFonts="1">
+  <fonts count="48" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3189,6 +3339,22 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -3216,7 +3382,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -3295,13 +3461,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3472,6 +3653,30 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="23" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7917,6 +8122,108 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>942975</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>914399</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4857750" cy="1269065"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1628775" y="914399"/>
+          <a:ext cx="4857750" cy="1269065"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>웹소켓 요청</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>{</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>   type: '1' : dashboard , '2': 'jobing', '8':</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>모의서버 시작 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t> '9': </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>모의서버 중지</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>  payload : { }</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>   reqdate:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>}</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
@@ -8763,7 +9070,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
@@ -8772,46 +9079,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="9" t="s">
-        <v>379</v>
-      </c>
+      <c r="B1" s="9"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
-        <v>372</v>
-      </c>
-      <c r="B2" s="38" t="s">
-        <v>373</v>
-      </c>
-      <c r="C2" s="38" t="s">
-        <v>374</v>
-      </c>
-      <c r="D2" s="38" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>376</v>
-      </c>
-      <c r="C3" t="s">
-        <v>377</v>
-      </c>
-      <c r="D3" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>2</v>
-      </c>
+      <c r="A2" s="38"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8829,23 +9108,23 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="54" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="B1" s="54" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="C1" s="54" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="D1" s="55" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="E1" s="54" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="F1" s="54"/>
       <c r="G1" s="54" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="H1" s="54"/>
       <c r="I1" s="54"/>
@@ -8857,27 +9136,27 @@
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="47" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="F2" s="47" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="H2" s="47" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="I2" s="47" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="J2" s="47" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="42" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="B3" s="42"/>
       <c r="C3" s="42"/>
@@ -8894,10 +9173,10 @@
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="42"/>
       <c r="B4" s="42" t="s">
+        <v>404</v>
+      </c>
+      <c r="C4" s="42" t="s">
         <v>412</v>
-      </c>
-      <c r="C4" s="42" t="s">
-        <v>420</v>
       </c>
       <c r="D4" s="40"/>
       <c r="E4" s="40"/>
@@ -8910,10 +9189,10 @@
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="42"/>
       <c r="B5" s="42" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="D5" s="40"/>
       <c r="E5" s="40"/>
@@ -8925,7 +9204,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="42" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="B6" s="42"/>
       <c r="C6" s="42"/>
@@ -8942,11 +9221,11 @@
     <row r="7" spans="1:10" s="51" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="48"/>
       <c r="B7" s="48" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="C7" s="48"/>
       <c r="D7" s="49" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="E7" s="49"/>
       <c r="F7" s="49"/>
@@ -8958,10 +9237,10 @@
     <row r="8" spans="1:10" s="51" customFormat="1" ht="66" x14ac:dyDescent="0.3">
       <c r="A8" s="48"/>
       <c r="B8" s="48" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="D8" s="53"/>
       <c r="E8" s="49"/>
@@ -8974,10 +9253,10 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="42"/>
       <c r="B9" s="42" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="C9" s="43" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="D9" s="44"/>
       <c r="E9" s="40"/>
@@ -8990,10 +9269,10 @@
     <row r="10" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A10" s="42"/>
       <c r="B10" s="42" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="C10" s="43" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="D10" s="44"/>
       <c r="E10" s="40"/>
@@ -9005,7 +9284,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="42" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="B11" s="42"/>
       <c r="C11" s="42"/>
@@ -9028,10 +9307,10 @@
     <row r="12" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A12" s="42"/>
       <c r="B12" s="42" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="C12" s="43" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="D12" s="44"/>
       <c r="E12" s="40"/>
@@ -9044,13 +9323,13 @@
     <row r="13" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="42"/>
       <c r="B13" s="42" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C13" s="43" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="E13" s="40"/>
       <c r="F13" s="40"/>
@@ -9061,7 +9340,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="42" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="B14" s="42"/>
       <c r="C14" s="42"/>
@@ -9076,10 +9355,10 @@
     <row r="15" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A15" s="42"/>
       <c r="B15" s="42" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="C15" s="43" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="D15" s="44"/>
       <c r="E15" s="40"/>
@@ -9100,13 +9379,13 @@
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="42"/>
       <c r="B16" s="42" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="D16" s="44" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="E16" s="40"/>
       <c r="F16" s="40"/>
@@ -9117,7 +9396,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="42" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="B17" s="42"/>
       <c r="C17" s="42"/>
@@ -9142,10 +9421,10 @@
     <row r="18" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A18" s="42"/>
       <c r="B18" s="42" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C18" s="43" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="D18" s="44"/>
       <c r="E18" s="40"/>
@@ -9158,10 +9437,10 @@
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="42"/>
       <c r="B19" s="42" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="C19" s="43" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="D19" s="44"/>
       <c r="E19" s="40"/>
@@ -9174,13 +9453,13 @@
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="42"/>
       <c r="B20" s="42" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="C20" s="43" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="D20" s="44" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="E20" s="40"/>
       <c r="F20" s="40"/>
@@ -9191,7 +9470,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="46" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="B21" s="45"/>
       <c r="C21" s="45"/>
@@ -9232,6 +9511,774 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M43"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.5" style="58" customWidth="1"/>
+    <col min="2" max="3" width="10.875" customWidth="1"/>
+    <col min="4" max="4" width="9.5" customWidth="1"/>
+    <col min="5" max="5" width="11.75" customWidth="1"/>
+    <col min="6" max="6" width="10.25" customWidth="1"/>
+    <col min="7" max="7" width="11.875" customWidth="1"/>
+    <col min="8" max="9" width="11.5" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="10.875" customWidth="1"/>
+    <col min="12" max="12" width="12.125" customWidth="1"/>
+    <col min="13" max="13" width="11.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="64" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="59" t="s">
+        <v>446</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>447</v>
+      </c>
+      <c r="C2" s="59" t="s">
+        <v>475</v>
+      </c>
+      <c r="D2" s="59" t="s">
+        <v>455</v>
+      </c>
+      <c r="E2" s="59" t="s">
+        <v>448</v>
+      </c>
+      <c r="F2" s="59" t="s">
+        <v>449</v>
+      </c>
+      <c r="G2" s="59" t="s">
+        <v>451</v>
+      </c>
+      <c r="H2" s="59" t="s">
+        <v>450</v>
+      </c>
+      <c r="I2" s="59" t="s">
+        <v>479</v>
+      </c>
+      <c r="J2" s="59" t="s">
+        <v>452</v>
+      </c>
+      <c r="K2" s="59" t="s">
+        <v>453</v>
+      </c>
+      <c r="L2" s="59" t="s">
+        <v>454</v>
+      </c>
+      <c r="M2" s="59" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="B3" s="61" t="s">
+        <v>457</v>
+      </c>
+      <c r="C3" s="61" t="s">
+        <v>476</v>
+      </c>
+      <c r="D3" s="61" t="s">
+        <v>458</v>
+      </c>
+      <c r="E3" s="62">
+        <v>46082</v>
+      </c>
+      <c r="F3" s="60"/>
+      <c r="G3" s="62">
+        <v>46084</v>
+      </c>
+      <c r="H3" s="62">
+        <v>46084</v>
+      </c>
+      <c r="I3" s="62" t="s">
+        <v>480</v>
+      </c>
+      <c r="J3" s="62">
+        <v>46085</v>
+      </c>
+      <c r="K3" s="60" t="s">
+        <v>459</v>
+      </c>
+      <c r="L3" s="62">
+        <v>46086</v>
+      </c>
+      <c r="M3" s="61" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="60"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="60" t="s">
+        <v>460</v>
+      </c>
+      <c r="L4" s="62"/>
+      <c r="M4" s="61"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="60"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="60" t="s">
+        <v>461</v>
+      </c>
+      <c r="L5" s="62"/>
+      <c r="M5" s="61"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="60"/>
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="60" t="s">
+        <v>462</v>
+      </c>
+      <c r="L6" s="62">
+        <v>46086</v>
+      </c>
+      <c r="M6" s="61" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="60"/>
+      <c r="B7" s="61"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="62">
+        <v>46091</v>
+      </c>
+      <c r="F7" s="60"/>
+      <c r="G7" s="62">
+        <v>46092</v>
+      </c>
+      <c r="H7" s="62">
+        <v>46092</v>
+      </c>
+      <c r="I7" s="62" t="s">
+        <v>480</v>
+      </c>
+      <c r="J7" s="62"/>
+      <c r="K7" s="60" t="s">
+        <v>459</v>
+      </c>
+      <c r="L7" s="62"/>
+      <c r="M7" s="61"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="60"/>
+      <c r="B8" s="61"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="62"/>
+      <c r="K8" s="60" t="s">
+        <v>460</v>
+      </c>
+      <c r="L8" s="62"/>
+      <c r="M8" s="61"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="60"/>
+      <c r="B9" s="61"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="62"/>
+      <c r="H9" s="62"/>
+      <c r="I9" s="62"/>
+      <c r="J9" s="62"/>
+      <c r="K9" s="60" t="s">
+        <v>461</v>
+      </c>
+      <c r="L9" s="62"/>
+      <c r="M9" s="61"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="60"/>
+      <c r="B10" s="61"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="62"/>
+      <c r="K10" s="60" t="s">
+        <v>462</v>
+      </c>
+      <c r="L10" s="62"/>
+      <c r="M10" s="61" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="B11" s="61" t="s">
+        <v>463</v>
+      </c>
+      <c r="C11" s="61" t="s">
+        <v>477</v>
+      </c>
+      <c r="D11" s="61"/>
+      <c r="E11" s="62">
+        <v>46082</v>
+      </c>
+      <c r="F11" s="60"/>
+      <c r="G11" s="62">
+        <v>46084</v>
+      </c>
+      <c r="H11" s="62">
+        <v>46084</v>
+      </c>
+      <c r="I11" s="62" t="s">
+        <v>481</v>
+      </c>
+      <c r="J11" s="62">
+        <v>46085</v>
+      </c>
+      <c r="K11" s="60" t="s">
+        <v>459</v>
+      </c>
+      <c r="L11" s="62">
+        <v>46086</v>
+      </c>
+      <c r="M11" s="61" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="60"/>
+      <c r="B12" s="61"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="62"/>
+      <c r="H12" s="62"/>
+      <c r="I12" s="62"/>
+      <c r="J12" s="62"/>
+      <c r="K12" s="60" t="s">
+        <v>460</v>
+      </c>
+      <c r="L12" s="62"/>
+      <c r="M12" s="61"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="60"/>
+      <c r="B13" s="61"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="62"/>
+      <c r="K13" s="60" t="s">
+        <v>462</v>
+      </c>
+      <c r="L13" s="62">
+        <v>46086</v>
+      </c>
+      <c r="M13" s="61" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="60"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="62">
+        <v>46091</v>
+      </c>
+      <c r="F14" s="60"/>
+      <c r="G14" s="62">
+        <v>46092</v>
+      </c>
+      <c r="H14" s="62">
+        <v>46092</v>
+      </c>
+      <c r="I14" s="62" t="s">
+        <v>481</v>
+      </c>
+      <c r="J14" s="62"/>
+      <c r="K14" s="60" t="s">
+        <v>459</v>
+      </c>
+      <c r="L14" s="62"/>
+      <c r="M14" s="61"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="60"/>
+      <c r="B15" s="61"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="62"/>
+      <c r="K15" s="60" t="s">
+        <v>460</v>
+      </c>
+      <c r="L15" s="62"/>
+      <c r="M15" s="61"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="60"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="62"/>
+      <c r="H16" s="62"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="62"/>
+      <c r="K16" s="60" t="s">
+        <v>461</v>
+      </c>
+      <c r="L16" s="62"/>
+      <c r="M16" s="61"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="60"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="62"/>
+      <c r="H17" s="62"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="62"/>
+      <c r="K17" s="60" t="s">
+        <v>462</v>
+      </c>
+      <c r="L17" s="62"/>
+      <c r="M17" s="61" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="B18" s="63" t="s">
+        <v>464</v>
+      </c>
+      <c r="C18" s="61" t="s">
+        <v>478</v>
+      </c>
+      <c r="D18" s="61" t="s">
+        <v>470</v>
+      </c>
+      <c r="E18" s="62">
+        <v>46082</v>
+      </c>
+      <c r="F18" s="60"/>
+      <c r="G18" s="62">
+        <v>46084</v>
+      </c>
+      <c r="H18" s="62">
+        <v>46084</v>
+      </c>
+      <c r="I18" s="62" t="s">
+        <v>482</v>
+      </c>
+      <c r="J18" s="62">
+        <v>46085</v>
+      </c>
+      <c r="K18" s="60" t="s">
+        <v>490</v>
+      </c>
+      <c r="L18" s="62">
+        <v>46086</v>
+      </c>
+      <c r="M18" s="61" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="60"/>
+      <c r="B19" s="61"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="62">
+        <v>46090</v>
+      </c>
+      <c r="F19" s="60" t="s">
+        <v>465</v>
+      </c>
+      <c r="G19" s="62"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="62"/>
+      <c r="K19" s="60"/>
+      <c r="L19" s="62"/>
+      <c r="M19" s="61"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="60" t="s">
+        <v>483</v>
+      </c>
+      <c r="B20" s="61" t="s">
+        <v>484</v>
+      </c>
+      <c r="C20" s="61" t="s">
+        <v>485</v>
+      </c>
+      <c r="D20" s="61" t="s">
+        <v>486</v>
+      </c>
+      <c r="E20" s="62">
+        <v>46083</v>
+      </c>
+      <c r="F20" s="60"/>
+      <c r="G20" s="62">
+        <v>46092</v>
+      </c>
+      <c r="H20" s="62">
+        <v>46092</v>
+      </c>
+      <c r="I20" s="62" t="s">
+        <v>487</v>
+      </c>
+      <c r="J20" s="62">
+        <v>46092</v>
+      </c>
+      <c r="K20" s="60" t="s">
+        <v>488</v>
+      </c>
+      <c r="L20" s="62">
+        <v>46092</v>
+      </c>
+      <c r="M20" s="61" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="60"/>
+      <c r="B21" s="61"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="62"/>
+      <c r="K21" s="60"/>
+      <c r="L21" s="62"/>
+      <c r="M21" s="61"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="60"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="60"/>
+      <c r="L22" s="62"/>
+      <c r="M22" s="61"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" s="60"/>
+      <c r="B23" s="61"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="62"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="62"/>
+      <c r="M23" s="61"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" s="60"/>
+      <c r="B24" s="61"/>
+      <c r="C24" s="61"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="62"/>
+      <c r="F24" s="60"/>
+      <c r="G24" s="62"/>
+      <c r="H24" s="62"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="62"/>
+      <c r="K24" s="60"/>
+      <c r="L24" s="62"/>
+      <c r="M24" s="61"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" s="60"/>
+      <c r="B25" s="61"/>
+      <c r="C25" s="61"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="60"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="62"/>
+      <c r="I25" s="62"/>
+      <c r="J25" s="62"/>
+      <c r="K25" s="60"/>
+      <c r="L25" s="62"/>
+      <c r="M25" s="61"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" s="60"/>
+      <c r="B26" s="61"/>
+      <c r="C26" s="61"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="62"/>
+      <c r="I26" s="62"/>
+      <c r="J26" s="62"/>
+      <c r="K26" s="60"/>
+      <c r="L26" s="62"/>
+      <c r="M26" s="61"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27" s="60"/>
+      <c r="B27" s="61"/>
+      <c r="C27" s="61"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="62"/>
+      <c r="H27" s="62"/>
+      <c r="I27" s="62"/>
+      <c r="J27" s="62"/>
+      <c r="K27" s="60"/>
+      <c r="L27" s="62"/>
+      <c r="M27" s="61"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" s="60"/>
+      <c r="B28" s="61"/>
+      <c r="C28" s="61"/>
+      <c r="D28" s="61"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="60"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="62"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="62"/>
+      <c r="K28" s="60"/>
+      <c r="L28" s="62"/>
+      <c r="M28" s="61"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" s="60"/>
+      <c r="B29" s="61"/>
+      <c r="C29" s="61"/>
+      <c r="D29" s="61"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="60"/>
+      <c r="G29" s="62"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="62"/>
+      <c r="J29" s="62"/>
+      <c r="K29" s="60"/>
+      <c r="L29" s="62"/>
+      <c r="M29" s="61"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E30" s="57"/>
+      <c r="F30" s="58"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="58"/>
+      <c r="L30" s="57"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E31" s="57"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="57"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="58"/>
+      <c r="L31" s="57"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E32" s="57"/>
+      <c r="F32" s="58"/>
+      <c r="G32" s="57"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="57"/>
+      <c r="J32" s="57"/>
+      <c r="K32" s="58"/>
+      <c r="L32" s="57"/>
+    </row>
+    <row r="33" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="E33" s="57"/>
+      <c r="F33" s="58"/>
+      <c r="G33" s="57"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="58"/>
+      <c r="L33" s="57"/>
+    </row>
+    <row r="34" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="E34" s="57"/>
+      <c r="F34" s="58"/>
+      <c r="G34" s="57"/>
+      <c r="H34" s="57"/>
+      <c r="I34" s="57"/>
+      <c r="J34" s="57"/>
+      <c r="K34" s="58"/>
+      <c r="L34" s="57"/>
+    </row>
+    <row r="35" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="E35" s="57"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="57"/>
+      <c r="H35" s="57"/>
+      <c r="I35" s="57"/>
+      <c r="J35" s="57"/>
+      <c r="K35" s="58"/>
+      <c r="L35" s="57"/>
+    </row>
+    <row r="36" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="E36" s="57"/>
+      <c r="F36" s="58"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="58"/>
+      <c r="L36" s="57"/>
+    </row>
+    <row r="37" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="E37" s="57"/>
+      <c r="F37" s="58"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="58"/>
+      <c r="L37" s="57"/>
+    </row>
+    <row r="38" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="E38" s="57"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="57"/>
+      <c r="H38" s="57"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="58"/>
+      <c r="L38" s="57"/>
+    </row>
+    <row r="39" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="E39" s="57"/>
+      <c r="F39" s="58"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="57"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="58"/>
+      <c r="L39" s="57"/>
+    </row>
+    <row r="40" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="E40" s="57"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="58"/>
+      <c r="L40" s="57"/>
+    </row>
+    <row r="41" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="E41" s="57"/>
+      <c r="F41" s="58"/>
+      <c r="G41" s="57"/>
+      <c r="H41" s="57"/>
+      <c r="I41" s="57"/>
+      <c r="J41" s="57"/>
+      <c r="K41" s="58"/>
+      <c r="L41" s="57"/>
+    </row>
+    <row r="42" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="E42" s="57"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="57"/>
+      <c r="H42" s="57"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="57"/>
+      <c r="K42" s="58"/>
+      <c r="L42" s="57"/>
+    </row>
+    <row r="43" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="E43" s="58"/>
+      <c r="F43" s="58"/>
+      <c r="G43" s="58"/>
+      <c r="H43" s="58"/>
+      <c r="I43" s="58"/>
+      <c r="J43" s="58"/>
+      <c r="K43" s="58"/>
+      <c r="L43" s="58"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10487,7 +11534,7 @@
       <c r="B7" s="34"/>
       <c r="C7" s="35"/>
       <c r="D7" s="35" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -10501,49 +11548,49 @@
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="33"/>
       <c r="B9" s="34" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="C9" s="35" t="s">
         <v>36</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="33"/>
       <c r="B10" s="34" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C10" s="35" t="s">
         <v>35</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="33"/>
       <c r="B11" s="34" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="D11" s="35" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="33"/>
       <c r="B12" s="34" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="C12" s="35" t="s">
         <v>39</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -10643,7 +11690,7 @@
         <v>69</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -10655,7 +11702,7 @@
         <v>70</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="37.5" x14ac:dyDescent="0.3">
@@ -10902,7 +11949,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="37" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="B14" s="2"/>
     </row>
@@ -10916,42 +11963,42 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="37" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="37" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="37" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="37" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="37" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -10959,7 +12006,7 @@
         <v>367</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -10967,7 +12014,7 @@
         <v>368</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -10975,31 +12022,31 @@
         <v>369</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="37" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="37" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="37" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -11007,7 +12054,7 @@
         <v>370</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -11176,7 +12223,7 @@
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="24" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>

--- a/aqt_docs.xlsx
+++ b/aqt_docs.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28380" windowHeight="11325" firstSheet="3" activeTab="11"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28380" windowHeight="11325" firstSheet="3" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="사용법" sheetId="4" r:id="rId1"/>
@@ -22,8 +22,9 @@
     <sheet name="tmax실행구조" sheetId="8" r:id="rId8"/>
     <sheet name="기타환경변수" sheetId="3" r:id="rId9"/>
     <sheet name="Sheet1" sheetId="9" r:id="rId10"/>
-    <sheet name="Sheet3" sheetId="11" r:id="rId11"/>
-    <sheet name="Sheet2" sheetId="12" r:id="rId12"/>
+    <sheet name="BC" sheetId="13" r:id="rId11"/>
+    <sheet name="Sheet3" sheetId="11" r:id="rId12"/>
+    <sheet name="Sheet2" sheetId="12" r:id="rId13"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="509">
   <si>
     <t>tapphosts</t>
   </si>
@@ -2709,10 +2710,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>테스트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AQT 테스트</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2987,6 +2984,82 @@
   </si>
   <si>
     <t>U2L 전환 및 테스트 현황</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>온라인테스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>거래로그 활용가능여부
+테스트데이터 변환 커스터마이징
+네트워크 캡쳐검토 
+테스트데이터 작성방법 정의</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>누락서비스 테스트데이터 입력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트데이터 관리 ( 수집/입력/검증)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">로그에서 수집되지않은 서비스 데이터 수동입력 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트 결과 보고서 생성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수행결과 리포팅 및 검토</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문제 원인 분석 및 해결방안 도출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트 환경검토 및 준비
+자동화 테스트 수행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>온라인테스트( JAVA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통합채널 온라인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BXM 온라인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통합채널 배치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BXM 배치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SQL 온라인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SQL 배치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>43개 SUB업무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>업무의 규모 및 복잡도에 따라 조정됨</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2994,7 +3067,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="48" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="52" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3355,8 +3431,42 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF002060"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3378,6 +3488,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3477,12 +3593,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3645,15 +3764,6 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3678,8 +3788,72 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="45" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -9096,10 +9270,514 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J34"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.75" style="51" customWidth="1"/>
+    <col min="2" max="2" width="30.125" style="51" customWidth="1"/>
+    <col min="3" max="3" width="46.375" style="78" customWidth="1"/>
+    <col min="4" max="4" width="11.875" style="51" customWidth="1"/>
+    <col min="5" max="9" width="6.375" style="51" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="51"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="69" t="s">
+        <v>436</v>
+      </c>
+      <c r="B1" s="69" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1" s="76" t="s">
+        <v>438</v>
+      </c>
+      <c r="D1" s="70" t="s">
+        <v>441</v>
+      </c>
+      <c r="E1" s="69" t="s">
+        <v>435</v>
+      </c>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69" t="s">
+        <v>434</v>
+      </c>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+    </row>
+    <row r="2" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="69"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="72" t="s">
+        <v>428</v>
+      </c>
+      <c r="F2" s="72" t="s">
+        <v>429</v>
+      </c>
+      <c r="G2" s="72" t="s">
+        <v>430</v>
+      </c>
+      <c r="H2" s="72" t="s">
+        <v>431</v>
+      </c>
+      <c r="I2" s="72" t="s">
+        <v>432</v>
+      </c>
+      <c r="J2" s="69"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="73" t="s">
+        <v>403</v>
+      </c>
+      <c r="B3" s="73"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49">
+        <v>2</v>
+      </c>
+      <c r="F3" s="49"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="73"/>
+      <c r="B4" s="73" t="s">
+        <v>404</v>
+      </c>
+      <c r="C4" s="52" t="s">
+        <v>412</v>
+      </c>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="73"/>
+      <c r="B5" s="73" t="s">
+        <v>405</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>406</v>
+      </c>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="73" t="s">
+        <v>407</v>
+      </c>
+      <c r="B6" s="73"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49">
+        <v>2</v>
+      </c>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="73"/>
+      <c r="B7" s="73" t="s">
+        <v>444</v>
+      </c>
+      <c r="C7" s="52"/>
+      <c r="D7" s="49" t="s">
+        <v>440</v>
+      </c>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+    </row>
+    <row r="8" spans="1:10" ht="66" x14ac:dyDescent="0.3">
+      <c r="A8" s="73"/>
+      <c r="B8" s="73" t="s">
+        <v>414</v>
+      </c>
+      <c r="C8" s="52" t="s">
+        <v>413</v>
+      </c>
+      <c r="D8" s="53"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="81"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="73"/>
+      <c r="B9" s="73" t="s">
+        <v>415</v>
+      </c>
+      <c r="C9" s="52" t="s">
+        <v>416</v>
+      </c>
+      <c r="D9" s="53"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="81"/>
+    </row>
+    <row r="10" spans="1:10" ht="66" x14ac:dyDescent="0.3">
+      <c r="A10" s="73"/>
+      <c r="B10" s="73" t="s">
+        <v>408</v>
+      </c>
+      <c r="C10" s="52" t="s">
+        <v>492</v>
+      </c>
+      <c r="D10" s="53"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="73" t="s">
+        <v>494</v>
+      </c>
+      <c r="B11" s="73"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49">
+        <v>1</v>
+      </c>
+      <c r="G11" s="81">
+        <v>1</v>
+      </c>
+      <c r="H11" s="81">
+        <v>1</v>
+      </c>
+      <c r="I11" s="81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+      <c r="A12" s="73"/>
+      <c r="B12" s="73" t="s">
+        <v>418</v>
+      </c>
+      <c r="C12" s="52" t="s">
+        <v>419</v>
+      </c>
+      <c r="D12" s="53"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="73"/>
+      <c r="B13" s="73" t="s">
+        <v>493</v>
+      </c>
+      <c r="C13" s="52" t="s">
+        <v>495</v>
+      </c>
+      <c r="D13" s="53" t="s">
+        <v>442</v>
+      </c>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81"/>
+    </row>
+    <row r="14" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="73"/>
+      <c r="B14" s="73" t="s">
+        <v>420</v>
+      </c>
+      <c r="C14" s="52" t="s">
+        <v>421</v>
+      </c>
+      <c r="D14" s="53" t="s">
+        <v>442</v>
+      </c>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="81"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="73" t="s">
+        <v>500</v>
+      </c>
+      <c r="B15" s="73"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="81"/>
+      <c r="I15" s="81"/>
+    </row>
+    <row r="16" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+      <c r="A16" s="73"/>
+      <c r="B16" s="73" t="s">
+        <v>422</v>
+      </c>
+      <c r="C16" s="52" t="s">
+        <v>499</v>
+      </c>
+      <c r="D16" s="53"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="81">
+        <v>1</v>
+      </c>
+      <c r="H16" s="81">
+        <v>1</v>
+      </c>
+      <c r="I16" s="81"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="73"/>
+      <c r="B17" s="73" t="s">
+        <v>496</v>
+      </c>
+      <c r="C17" s="52" t="s">
+        <v>497</v>
+      </c>
+      <c r="D17" s="53"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="81">
+        <v>1</v>
+      </c>
+      <c r="H17" s="81">
+        <v>1</v>
+      </c>
+      <c r="I17" s="81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="73"/>
+      <c r="B18" s="65" t="s">
+        <v>498</v>
+      </c>
+      <c r="C18" s="66" t="s">
+        <v>426</v>
+      </c>
+      <c r="D18" s="67" t="s">
+        <v>442</v>
+      </c>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="82"/>
+      <c r="H18" s="82"/>
+      <c r="I18" s="82"/>
+      <c r="J18" s="79" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="73" t="s">
+        <v>443</v>
+      </c>
+      <c r="B19" s="73"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="81"/>
+      <c r="H19" s="81"/>
+      <c r="I19" s="81"/>
+    </row>
+    <row r="20" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="73"/>
+      <c r="B20" s="73" t="s">
+        <v>409</v>
+      </c>
+      <c r="C20" s="52" t="s">
+        <v>410</v>
+      </c>
+      <c r="D20" s="53"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49">
+        <v>1</v>
+      </c>
+      <c r="G20" s="81"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="81"/>
+    </row>
+    <row r="21" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+      <c r="A21" s="73"/>
+      <c r="B21" s="73" t="s">
+        <v>423</v>
+      </c>
+      <c r="C21" s="52" t="s">
+        <v>424</v>
+      </c>
+      <c r="D21" s="53"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="81">
+        <v>1</v>
+      </c>
+      <c r="H21" s="81">
+        <v>1</v>
+      </c>
+      <c r="I21" s="81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="73"/>
+      <c r="B22" s="65" t="s">
+        <v>425</v>
+      </c>
+      <c r="C22" s="66" t="s">
+        <v>426</v>
+      </c>
+      <c r="D22" s="67" t="s">
+        <v>442</v>
+      </c>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="82"/>
+      <c r="H22" s="82"/>
+      <c r="I22" s="82"/>
+      <c r="J22" s="79" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="74" t="s">
+        <v>439</v>
+      </c>
+      <c r="B23" s="75"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="72">
+        <f t="shared" ref="E23:F23" si="0">SUM(E3:E21)</f>
+        <v>2</v>
+      </c>
+      <c r="F23" s="72">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G23" s="72">
+        <f>SUM(G3:G22)</f>
+        <v>4</v>
+      </c>
+      <c r="H23" s="72">
+        <f>SUM(H3:H22)</f>
+        <v>4</v>
+      </c>
+      <c r="I23" s="72">
+        <f>SUM(I3:I22)</f>
+        <v>3</v>
+      </c>
+      <c r="J23" s="51">
+        <f>SUM(E23:I23)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="51" t="s">
+        <v>501</v>
+      </c>
+      <c r="D25" s="80">
+        <f>1687+5809+7451</f>
+        <v>14947</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="78" t="s">
+        <v>502</v>
+      </c>
+      <c r="D26" s="80">
+        <v>8404</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D27" s="80"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C28" s="78" t="s">
+        <v>503</v>
+      </c>
+      <c r="D28" s="80">
+        <f>6544+613+1421</f>
+        <v>8578</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="78" t="s">
+        <v>504</v>
+      </c>
+      <c r="D29" s="80">
+        <v>5511</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D30" s="80"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="78" t="s">
+        <v>505</v>
+      </c>
+      <c r="D31" s="80">
+        <f>31438+32761</f>
+        <v>64199</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C32" s="78" t="s">
+        <v>506</v>
+      </c>
+      <c r="D32" s="80">
+        <f>20244+30315</f>
+        <v>50559</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C34" s="78" t="s">
+        <v>507</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:I1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.625" customWidth="1"/>
+    <col min="1" max="1" width="19.125" customWidth="1"/>
     <col min="2" max="2" width="24.75" customWidth="1"/>
     <col min="3" max="3" width="60.375" customWidth="1"/>
     <col min="4" max="4" width="11.875" customWidth="1"/>
@@ -9107,51 +9785,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="62" t="s">
+        <v>436</v>
+      </c>
+      <c r="B1" s="62" t="s">
         <v>437</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="C1" s="62" t="s">
         <v>438</v>
       </c>
-      <c r="C1" s="54" t="s">
-        <v>439</v>
-      </c>
-      <c r="D1" s="55" t="s">
-        <v>442</v>
-      </c>
-      <c r="E1" s="54" t="s">
-        <v>436</v>
-      </c>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54" t="s">
+      <c r="D1" s="63" t="s">
+        <v>441</v>
+      </c>
+      <c r="E1" s="62" t="s">
         <v>435</v>
       </c>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62" t="s">
+        <v>434</v>
+      </c>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
     </row>
     <row r="2" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="54"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="56"/>
+      <c r="A2" s="62"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="64"/>
       <c r="E2" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="F2" s="47" t="s">
         <v>429</v>
       </c>
-      <c r="F2" s="47" t="s">
+      <c r="G2" s="47" t="s">
         <v>430</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="H2" s="47" t="s">
         <v>431</v>
       </c>
-      <c r="H2" s="47" t="s">
+      <c r="I2" s="47" t="s">
         <v>432</v>
       </c>
-      <c r="I2" s="47" t="s">
+      <c r="J2" s="47" t="s">
         <v>433</v>
-      </c>
-      <c r="J2" s="47" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -9221,11 +9899,11 @@
     <row r="7" spans="1:10" s="51" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="48"/>
       <c r="B7" s="48" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C7" s="48"/>
       <c r="D7" s="49" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E7" s="49"/>
       <c r="F7" s="49"/>
@@ -9329,7 +10007,7 @@
         <v>421</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E13" s="40"/>
       <c r="F13" s="40"/>
@@ -9340,7 +10018,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="42" t="s">
-        <v>422</v>
+        <v>491</v>
       </c>
       <c r="B14" s="42"/>
       <c r="C14" s="42"/>
@@ -9355,10 +10033,10 @@
     <row r="15" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A15" s="42"/>
       <c r="B15" s="42" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C15" s="43" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D15" s="44"/>
       <c r="E15" s="40"/>
@@ -9379,13 +10057,13 @@
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="42"/>
       <c r="B16" s="42" t="s">
+        <v>425</v>
+      </c>
+      <c r="C16" s="43" t="s">
         <v>426</v>
       </c>
-      <c r="C16" s="43" t="s">
-        <v>427</v>
-      </c>
       <c r="D16" s="44" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E16" s="40"/>
       <c r="F16" s="40"/>
@@ -9396,7 +10074,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="42" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B17" s="42"/>
       <c r="C17" s="42"/>
@@ -9437,10 +10115,10 @@
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="42"/>
       <c r="B19" s="42" t="s">
+        <v>423</v>
+      </c>
+      <c r="C19" s="43" t="s">
         <v>424</v>
-      </c>
-      <c r="C19" s="43" t="s">
-        <v>425</v>
       </c>
       <c r="D19" s="44"/>
       <c r="E19" s="40"/>
@@ -9453,13 +10131,13 @@
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="42"/>
       <c r="B20" s="42" t="s">
+        <v>425</v>
+      </c>
+      <c r="C20" s="43" t="s">
         <v>426</v>
       </c>
-      <c r="C20" s="43" t="s">
-        <v>427</v>
-      </c>
       <c r="D20" s="44" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E20" s="40"/>
       <c r="F20" s="40"/>
@@ -9470,7 +10148,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="46" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B21" s="45"/>
       <c r="C21" s="45"/>
@@ -9511,15 +10189,16 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M43"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.5" style="58" customWidth="1"/>
+    <col min="1" max="1" width="8.5" style="55" customWidth="1"/>
     <col min="2" max="3" width="10.875" customWidth="1"/>
     <col min="4" max="4" width="9.5" customWidth="1"/>
     <col min="5" max="5" width="11.75" customWidth="1"/>
@@ -9533,747 +10212,747 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E1" s="64" t="s">
-        <v>491</v>
+      <c r="E1" s="61" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="56" t="s">
+        <v>445</v>
+      </c>
+      <c r="B2" s="56" t="s">
         <v>446</v>
       </c>
-      <c r="B2" s="59" t="s">
+      <c r="C2" s="56" t="s">
+        <v>474</v>
+      </c>
+      <c r="D2" s="56" t="s">
+        <v>454</v>
+      </c>
+      <c r="E2" s="56" t="s">
         <v>447</v>
       </c>
-      <c r="C2" s="59" t="s">
+      <c r="F2" s="56" t="s">
+        <v>448</v>
+      </c>
+      <c r="G2" s="56" t="s">
+        <v>450</v>
+      </c>
+      <c r="H2" s="56" t="s">
+        <v>449</v>
+      </c>
+      <c r="I2" s="56" t="s">
+        <v>478</v>
+      </c>
+      <c r="J2" s="56" t="s">
+        <v>451</v>
+      </c>
+      <c r="K2" s="56" t="s">
+        <v>452</v>
+      </c>
+      <c r="L2" s="56" t="s">
+        <v>453</v>
+      </c>
+      <c r="M2" s="56" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="57" t="s">
+        <v>455</v>
+      </c>
+      <c r="B3" s="58" t="s">
+        <v>456</v>
+      </c>
+      <c r="C3" s="58" t="s">
         <v>475</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D3" s="58" t="s">
+        <v>457</v>
+      </c>
+      <c r="E3" s="59">
+        <v>46082</v>
+      </c>
+      <c r="F3" s="57"/>
+      <c r="G3" s="59">
+        <v>46084</v>
+      </c>
+      <c r="H3" s="59">
+        <v>46084</v>
+      </c>
+      <c r="I3" s="59" t="s">
+        <v>479</v>
+      </c>
+      <c r="J3" s="59">
+        <v>46085</v>
+      </c>
+      <c r="K3" s="57" t="s">
+        <v>458</v>
+      </c>
+      <c r="L3" s="59">
+        <v>46086</v>
+      </c>
+      <c r="M3" s="58" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="57"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="57" t="s">
+        <v>459</v>
+      </c>
+      <c r="L4" s="59"/>
+      <c r="M4" s="58"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="57"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="57" t="s">
+        <v>460</v>
+      </c>
+      <c r="L5" s="59"/>
+      <c r="M5" s="58"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="57"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="57" t="s">
+        <v>461</v>
+      </c>
+      <c r="L6" s="59">
+        <v>46086</v>
+      </c>
+      <c r="M6" s="58" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="57"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="59">
+        <v>46091</v>
+      </c>
+      <c r="F7" s="57"/>
+      <c r="G7" s="59">
+        <v>46092</v>
+      </c>
+      <c r="H7" s="59">
+        <v>46092</v>
+      </c>
+      <c r="I7" s="59" t="s">
+        <v>479</v>
+      </c>
+      <c r="J7" s="59"/>
+      <c r="K7" s="57" t="s">
+        <v>458</v>
+      </c>
+      <c r="L7" s="59"/>
+      <c r="M7" s="58"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="57"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="59"/>
+      <c r="K8" s="57" t="s">
+        <v>459</v>
+      </c>
+      <c r="L8" s="59"/>
+      <c r="M8" s="58"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="57"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="59"/>
+      <c r="K9" s="57" t="s">
+        <v>460</v>
+      </c>
+      <c r="L9" s="59"/>
+      <c r="M9" s="58"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="57"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="59"/>
+      <c r="K10" s="57" t="s">
+        <v>461</v>
+      </c>
+      <c r="L10" s="59"/>
+      <c r="M10" s="58" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="57" t="s">
         <v>455</v>
       </c>
-      <c r="E2" s="59" t="s">
-        <v>448</v>
-      </c>
-      <c r="F2" s="59" t="s">
-        <v>449</v>
-      </c>
-      <c r="G2" s="59" t="s">
-        <v>451</v>
-      </c>
-      <c r="H2" s="59" t="s">
-        <v>450</v>
-      </c>
-      <c r="I2" s="59" t="s">
-        <v>479</v>
-      </c>
-      <c r="J2" s="59" t="s">
-        <v>452</v>
-      </c>
-      <c r="K2" s="59" t="s">
-        <v>453</v>
-      </c>
-      <c r="L2" s="59" t="s">
-        <v>454</v>
-      </c>
-      <c r="M2" s="59" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="B3" s="61" t="s">
-        <v>457</v>
-      </c>
-      <c r="C3" s="61" t="s">
+      <c r="B11" s="58" t="s">
+        <v>462</v>
+      </c>
+      <c r="C11" s="58" t="s">
         <v>476</v>
       </c>
-      <c r="D3" s="61" t="s">
+      <c r="D11" s="58"/>
+      <c r="E11" s="59">
+        <v>46082</v>
+      </c>
+      <c r="F11" s="57"/>
+      <c r="G11" s="59">
+        <v>46084</v>
+      </c>
+      <c r="H11" s="59">
+        <v>46084</v>
+      </c>
+      <c r="I11" s="59" t="s">
+        <v>480</v>
+      </c>
+      <c r="J11" s="59">
+        <v>46085</v>
+      </c>
+      <c r="K11" s="57" t="s">
         <v>458</v>
       </c>
-      <c r="E3" s="62">
+      <c r="L11" s="59">
+        <v>46086</v>
+      </c>
+      <c r="M11" s="58" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="57"/>
+      <c r="B12" s="58"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="59"/>
+      <c r="K12" s="57" t="s">
+        <v>459</v>
+      </c>
+      <c r="L12" s="59"/>
+      <c r="M12" s="58"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="57"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="59"/>
+      <c r="J13" s="59"/>
+      <c r="K13" s="57" t="s">
+        <v>461</v>
+      </c>
+      <c r="L13" s="59">
+        <v>46086</v>
+      </c>
+      <c r="M13" s="58" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="57"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="59">
+        <v>46091</v>
+      </c>
+      <c r="F14" s="57"/>
+      <c r="G14" s="59">
+        <v>46092</v>
+      </c>
+      <c r="H14" s="59">
+        <v>46092</v>
+      </c>
+      <c r="I14" s="59" t="s">
+        <v>480</v>
+      </c>
+      <c r="J14" s="59"/>
+      <c r="K14" s="57" t="s">
+        <v>458</v>
+      </c>
+      <c r="L14" s="59"/>
+      <c r="M14" s="58"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="57"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="59"/>
+      <c r="I15" s="59"/>
+      <c r="J15" s="59"/>
+      <c r="K15" s="57" t="s">
+        <v>459</v>
+      </c>
+      <c r="L15" s="59"/>
+      <c r="M15" s="58"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="57"/>
+      <c r="B16" s="58"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="59"/>
+      <c r="I16" s="59"/>
+      <c r="J16" s="59"/>
+      <c r="K16" s="57" t="s">
+        <v>460</v>
+      </c>
+      <c r="L16" s="59"/>
+      <c r="M16" s="58"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="57"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="59"/>
+      <c r="J17" s="59"/>
+      <c r="K17" s="57" t="s">
+        <v>461</v>
+      </c>
+      <c r="L17" s="59"/>
+      <c r="M17" s="58" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" s="57" t="s">
+        <v>455</v>
+      </c>
+      <c r="B18" s="60" t="s">
+        <v>463</v>
+      </c>
+      <c r="C18" s="58" t="s">
+        <v>477</v>
+      </c>
+      <c r="D18" s="58" t="s">
+        <v>469</v>
+      </c>
+      <c r="E18" s="59">
         <v>46082</v>
       </c>
-      <c r="F3" s="60"/>
-      <c r="G3" s="62">
+      <c r="F18" s="57"/>
+      <c r="G18" s="59">
         <v>46084</v>
       </c>
-      <c r="H3" s="62">
+      <c r="H18" s="59">
         <v>46084</v>
       </c>
-      <c r="I3" s="62" t="s">
-        <v>480</v>
-      </c>
-      <c r="J3" s="62">
+      <c r="I18" s="59" t="s">
+        <v>481</v>
+      </c>
+      <c r="J18" s="59">
         <v>46085</v>
       </c>
-      <c r="K3" s="60" t="s">
-        <v>459</v>
-      </c>
-      <c r="L3" s="62">
+      <c r="K18" s="57" t="s">
+        <v>489</v>
+      </c>
+      <c r="L18" s="59">
         <v>46086</v>
       </c>
-      <c r="M3" s="61" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="60"/>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="60" t="s">
-        <v>460</v>
-      </c>
-      <c r="L4" s="62"/>
-      <c r="M4" s="61"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="60"/>
-      <c r="B5" s="61"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="60" t="s">
-        <v>461</v>
-      </c>
-      <c r="L5" s="62"/>
-      <c r="M5" s="61"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="60"/>
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="60" t="s">
-        <v>462</v>
-      </c>
-      <c r="L6" s="62">
-        <v>46086</v>
-      </c>
-      <c r="M6" s="61" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="60"/>
-      <c r="B7" s="61"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="62">
-        <v>46091</v>
-      </c>
-      <c r="F7" s="60"/>
-      <c r="G7" s="62">
+      <c r="M18" s="58" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="57"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="59">
+        <v>46090</v>
+      </c>
+      <c r="F19" s="57" t="s">
+        <v>464</v>
+      </c>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="59"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="59"/>
+      <c r="M19" s="58"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="57" t="s">
+        <v>482</v>
+      </c>
+      <c r="B20" s="58" t="s">
+        <v>483</v>
+      </c>
+      <c r="C20" s="58" t="s">
+        <v>484</v>
+      </c>
+      <c r="D20" s="58" t="s">
+        <v>485</v>
+      </c>
+      <c r="E20" s="59">
+        <v>46083</v>
+      </c>
+      <c r="F20" s="57"/>
+      <c r="G20" s="59">
         <v>46092</v>
       </c>
-      <c r="H7" s="62">
+      <c r="H20" s="59">
         <v>46092</v>
       </c>
-      <c r="I7" s="62" t="s">
-        <v>480</v>
-      </c>
-      <c r="J7" s="62"/>
-      <c r="K7" s="60" t="s">
-        <v>459</v>
-      </c>
-      <c r="L7" s="62"/>
-      <c r="M7" s="61"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="60"/>
-      <c r="B8" s="61"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="62"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="62"/>
-      <c r="K8" s="60" t="s">
-        <v>460</v>
-      </c>
-      <c r="L8" s="62"/>
-      <c r="M8" s="61"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="60"/>
-      <c r="B9" s="61"/>
-      <c r="C9" s="61"/>
-      <c r="D9" s="61"/>
-      <c r="E9" s="62"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="62"/>
-      <c r="H9" s="62"/>
-      <c r="I9" s="62"/>
-      <c r="J9" s="62"/>
-      <c r="K9" s="60" t="s">
-        <v>461</v>
-      </c>
-      <c r="L9" s="62"/>
-      <c r="M9" s="61"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="60"/>
-      <c r="B10" s="61"/>
-      <c r="C10" s="61"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="62"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="62"/>
-      <c r="J10" s="62"/>
-      <c r="K10" s="60" t="s">
-        <v>462</v>
-      </c>
-      <c r="L10" s="62"/>
-      <c r="M10" s="61" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="B11" s="61" t="s">
-        <v>463</v>
-      </c>
-      <c r="C11" s="61" t="s">
-        <v>477</v>
-      </c>
-      <c r="D11" s="61"/>
-      <c r="E11" s="62">
-        <v>46082</v>
-      </c>
-      <c r="F11" s="60"/>
-      <c r="G11" s="62">
-        <v>46084</v>
-      </c>
-      <c r="H11" s="62">
-        <v>46084</v>
-      </c>
-      <c r="I11" s="62" t="s">
-        <v>481</v>
-      </c>
-      <c r="J11" s="62">
-        <v>46085</v>
-      </c>
-      <c r="K11" s="60" t="s">
-        <v>459</v>
-      </c>
-      <c r="L11" s="62">
-        <v>46086</v>
-      </c>
-      <c r="M11" s="61" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="60"/>
-      <c r="B12" s="61"/>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="62"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="62"/>
-      <c r="H12" s="62"/>
-      <c r="I12" s="62"/>
-      <c r="J12" s="62"/>
-      <c r="K12" s="60" t="s">
-        <v>460</v>
-      </c>
-      <c r="L12" s="62"/>
-      <c r="M12" s="61"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="60"/>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="62"/>
-      <c r="K13" s="60" t="s">
-        <v>462</v>
-      </c>
-      <c r="L13" s="62">
-        <v>46086</v>
-      </c>
-      <c r="M13" s="61" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="60"/>
-      <c r="B14" s="61"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="62">
-        <v>46091</v>
-      </c>
-      <c r="F14" s="60"/>
-      <c r="G14" s="62">
+      <c r="I20" s="59" t="s">
+        <v>486</v>
+      </c>
+      <c r="J20" s="59">
         <v>46092</v>
       </c>
-      <c r="H14" s="62">
+      <c r="K20" s="57" t="s">
+        <v>487</v>
+      </c>
+      <c r="L20" s="59">
         <v>46092</v>
       </c>
-      <c r="I14" s="62" t="s">
-        <v>481</v>
-      </c>
-      <c r="J14" s="62"/>
-      <c r="K14" s="60" t="s">
-        <v>459</v>
-      </c>
-      <c r="L14" s="62"/>
-      <c r="M14" s="61"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="60"/>
-      <c r="B15" s="61"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="62"/>
-      <c r="I15" s="62"/>
-      <c r="J15" s="62"/>
-      <c r="K15" s="60" t="s">
-        <v>460</v>
-      </c>
-      <c r="L15" s="62"/>
-      <c r="M15" s="61"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="60"/>
-      <c r="B16" s="61"/>
-      <c r="C16" s="61"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="62"/>
-      <c r="H16" s="62"/>
-      <c r="I16" s="62"/>
-      <c r="J16" s="62"/>
-      <c r="K16" s="60" t="s">
-        <v>461</v>
-      </c>
-      <c r="L16" s="62"/>
-      <c r="M16" s="61"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="60"/>
-      <c r="B17" s="61"/>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="60" t="s">
-        <v>462</v>
-      </c>
-      <c r="L17" s="62"/>
-      <c r="M17" s="61" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="60" t="s">
-        <v>456</v>
-      </c>
-      <c r="B18" s="63" t="s">
-        <v>464</v>
-      </c>
-      <c r="C18" s="61" t="s">
-        <v>478</v>
-      </c>
-      <c r="D18" s="61" t="s">
-        <v>470</v>
-      </c>
-      <c r="E18" s="62">
-        <v>46082</v>
-      </c>
-      <c r="F18" s="60"/>
-      <c r="G18" s="62">
-        <v>46084</v>
-      </c>
-      <c r="H18" s="62">
-        <v>46084</v>
-      </c>
-      <c r="I18" s="62" t="s">
-        <v>482</v>
-      </c>
-      <c r="J18" s="62">
-        <v>46085</v>
-      </c>
-      <c r="K18" s="60" t="s">
-        <v>490</v>
-      </c>
-      <c r="L18" s="62">
-        <v>46086</v>
-      </c>
-      <c r="M18" s="61" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="60"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="62">
-        <v>46090</v>
-      </c>
-      <c r="F19" s="60" t="s">
-        <v>465</v>
-      </c>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="60"/>
-      <c r="L19" s="62"/>
-      <c r="M19" s="61"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="60" t="s">
-        <v>483</v>
-      </c>
-      <c r="B20" s="61" t="s">
-        <v>484</v>
-      </c>
-      <c r="C20" s="61" t="s">
-        <v>485</v>
-      </c>
-      <c r="D20" s="61" t="s">
-        <v>486</v>
-      </c>
-      <c r="E20" s="62">
-        <v>46083</v>
-      </c>
-      <c r="F20" s="60"/>
-      <c r="G20" s="62">
-        <v>46092</v>
-      </c>
-      <c r="H20" s="62">
-        <v>46092</v>
-      </c>
-      <c r="I20" s="62" t="s">
-        <v>487</v>
-      </c>
-      <c r="J20" s="62">
-        <v>46092</v>
-      </c>
-      <c r="K20" s="60" t="s">
+      <c r="M20" s="58" t="s">
         <v>488</v>
       </c>
-      <c r="L20" s="62">
-        <v>46092</v>
-      </c>
-      <c r="M20" s="61" t="s">
-        <v>489</v>
-      </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="60"/>
-      <c r="B21" s="61"/>
-      <c r="C21" s="61"/>
-      <c r="D21" s="61"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="60"/>
-      <c r="L21" s="62"/>
-      <c r="M21" s="61"/>
+      <c r="A21" s="57"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="59"/>
+      <c r="J21" s="59"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="59"/>
+      <c r="M21" s="58"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="60"/>
-      <c r="B22" s="61"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62"/>
-      <c r="K22" s="60"/>
-      <c r="L22" s="62"/>
-      <c r="M22" s="61"/>
+      <c r="A22" s="57"/>
+      <c r="B22" s="58"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="59"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="59"/>
+      <c r="J22" s="59"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="59"/>
+      <c r="M22" s="58"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="60"/>
-      <c r="B23" s="61"/>
-      <c r="C23" s="61"/>
-      <c r="D23" s="61"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="60"/>
-      <c r="L23" s="62"/>
-      <c r="M23" s="61"/>
+      <c r="A23" s="57"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="58"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="59"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="59"/>
+      <c r="M23" s="58"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="60"/>
-      <c r="B24" s="61"/>
-      <c r="C24" s="61"/>
-      <c r="D24" s="61"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="60"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="60"/>
-      <c r="L24" s="62"/>
-      <c r="M24" s="61"/>
+      <c r="A24" s="57"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="58"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="59"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="59"/>
+      <c r="J24" s="59"/>
+      <c r="K24" s="57"/>
+      <c r="L24" s="59"/>
+      <c r="M24" s="58"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" s="60"/>
-      <c r="B25" s="61"/>
-      <c r="C25" s="61"/>
-      <c r="D25" s="61"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="60"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="60"/>
-      <c r="L25" s="62"/>
-      <c r="M25" s="61"/>
+      <c r="A25" s="57"/>
+      <c r="B25" s="58"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="59"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="59"/>
+      <c r="M25" s="58"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" s="60"/>
-      <c r="B26" s="61"/>
-      <c r="C26" s="61"/>
-      <c r="D26" s="61"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="60"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="62"/>
-      <c r="K26" s="60"/>
-      <c r="L26" s="62"/>
-      <c r="M26" s="61"/>
+      <c r="A26" s="57"/>
+      <c r="B26" s="58"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="59"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="59"/>
+      <c r="M26" s="58"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" s="60"/>
-      <c r="B27" s="61"/>
-      <c r="C27" s="61"/>
-      <c r="D27" s="61"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="60"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="60"/>
-      <c r="L27" s="62"/>
-      <c r="M27" s="61"/>
+      <c r="A27" s="57"/>
+      <c r="B27" s="58"/>
+      <c r="C27" s="58"/>
+      <c r="D27" s="58"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="59"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="59"/>
+      <c r="M27" s="58"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A28" s="60"/>
-      <c r="B28" s="61"/>
-      <c r="C28" s="61"/>
-      <c r="D28" s="61"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="60"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="60"/>
-      <c r="L28" s="62"/>
-      <c r="M28" s="61"/>
+      <c r="A28" s="57"/>
+      <c r="B28" s="58"/>
+      <c r="C28" s="58"/>
+      <c r="D28" s="58"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="59"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="59"/>
+      <c r="K28" s="57"/>
+      <c r="L28" s="59"/>
+      <c r="M28" s="58"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A29" s="60"/>
-      <c r="B29" s="61"/>
-      <c r="C29" s="61"/>
-      <c r="D29" s="61"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="60"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="62"/>
-      <c r="K29" s="60"/>
-      <c r="L29" s="62"/>
-      <c r="M29" s="61"/>
+      <c r="A29" s="57"/>
+      <c r="B29" s="58"/>
+      <c r="C29" s="58"/>
+      <c r="D29" s="58"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="59"/>
+      <c r="J29" s="59"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="59"/>
+      <c r="M29" s="58"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E30" s="57"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="57"/>
-      <c r="K30" s="58"/>
-      <c r="L30" s="57"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="55"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="54"/>
+      <c r="J30" s="54"/>
+      <c r="K30" s="55"/>
+      <c r="L30" s="54"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E31" s="57"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="57"/>
-      <c r="H31" s="57"/>
-      <c r="I31" s="57"/>
-      <c r="J31" s="57"/>
-      <c r="K31" s="58"/>
-      <c r="L31" s="57"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="54"/>
+      <c r="J31" s="54"/>
+      <c r="K31" s="55"/>
+      <c r="L31" s="54"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E32" s="57"/>
-      <c r="F32" s="58"/>
-      <c r="G32" s="57"/>
-      <c r="H32" s="57"/>
-      <c r="I32" s="57"/>
-      <c r="J32" s="57"/>
-      <c r="K32" s="58"/>
-      <c r="L32" s="57"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="54"/>
+      <c r="J32" s="54"/>
+      <c r="K32" s="55"/>
+      <c r="L32" s="54"/>
     </row>
     <row r="33" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E33" s="57"/>
-      <c r="F33" s="58"/>
-      <c r="G33" s="57"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="57"/>
-      <c r="J33" s="57"/>
-      <c r="K33" s="58"/>
-      <c r="L33" s="57"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="54"/>
+      <c r="J33" s="54"/>
+      <c r="K33" s="55"/>
+      <c r="L33" s="54"/>
     </row>
     <row r="34" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E34" s="57"/>
-      <c r="F34" s="58"/>
-      <c r="G34" s="57"/>
-      <c r="H34" s="57"/>
-      <c r="I34" s="57"/>
-      <c r="J34" s="57"/>
-      <c r="K34" s="58"/>
-      <c r="L34" s="57"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="55"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="54"/>
+      <c r="J34" s="54"/>
+      <c r="K34" s="55"/>
+      <c r="L34" s="54"/>
     </row>
     <row r="35" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E35" s="57"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="57"/>
-      <c r="H35" s="57"/>
-      <c r="I35" s="57"/>
-      <c r="J35" s="57"/>
-      <c r="K35" s="58"/>
-      <c r="L35" s="57"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="55"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="54"/>
+      <c r="K35" s="55"/>
+      <c r="L35" s="54"/>
     </row>
     <row r="36" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E36" s="57"/>
-      <c r="F36" s="58"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="58"/>
-      <c r="L36" s="57"/>
+      <c r="E36" s="54"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="54"/>
+      <c r="I36" s="54"/>
+      <c r="J36" s="54"/>
+      <c r="K36" s="55"/>
+      <c r="L36" s="54"/>
     </row>
     <row r="37" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E37" s="57"/>
-      <c r="F37" s="58"/>
-      <c r="G37" s="57"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="57"/>
-      <c r="J37" s="57"/>
-      <c r="K37" s="58"/>
-      <c r="L37" s="57"/>
+      <c r="E37" s="54"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="54"/>
+      <c r="H37" s="54"/>
+      <c r="I37" s="54"/>
+      <c r="J37" s="54"/>
+      <c r="K37" s="55"/>
+      <c r="L37" s="54"/>
     </row>
     <row r="38" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E38" s="57"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="57"/>
-      <c r="H38" s="57"/>
-      <c r="I38" s="57"/>
-      <c r="J38" s="57"/>
-      <c r="K38" s="58"/>
-      <c r="L38" s="57"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="54"/>
+      <c r="I38" s="54"/>
+      <c r="J38" s="54"/>
+      <c r="K38" s="55"/>
+      <c r="L38" s="54"/>
     </row>
     <row r="39" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E39" s="57"/>
-      <c r="F39" s="58"/>
-      <c r="G39" s="57"/>
-      <c r="H39" s="57"/>
-      <c r="I39" s="57"/>
-      <c r="J39" s="57"/>
-      <c r="K39" s="58"/>
-      <c r="L39" s="57"/>
+      <c r="E39" s="54"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="54"/>
+      <c r="I39" s="54"/>
+      <c r="J39" s="54"/>
+      <c r="K39" s="55"/>
+      <c r="L39" s="54"/>
     </row>
     <row r="40" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E40" s="57"/>
-      <c r="F40" s="58"/>
-      <c r="G40" s="57"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="57"/>
-      <c r="J40" s="57"/>
-      <c r="K40" s="58"/>
-      <c r="L40" s="57"/>
+      <c r="E40" s="54"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="54"/>
+      <c r="H40" s="54"/>
+      <c r="I40" s="54"/>
+      <c r="J40" s="54"/>
+      <c r="K40" s="55"/>
+      <c r="L40" s="54"/>
     </row>
     <row r="41" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E41" s="57"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="57"/>
-      <c r="H41" s="57"/>
-      <c r="I41" s="57"/>
-      <c r="J41" s="57"/>
-      <c r="K41" s="58"/>
-      <c r="L41" s="57"/>
+      <c r="E41" s="54"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="54"/>
+      <c r="I41" s="54"/>
+      <c r="J41" s="54"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="54"/>
     </row>
     <row r="42" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E42" s="57"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="57"/>
-      <c r="H42" s="57"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="57"/>
-      <c r="K42" s="58"/>
-      <c r="L42" s="57"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="55"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="54"/>
+      <c r="I42" s="54"/>
+      <c r="J42" s="54"/>
+      <c r="K42" s="55"/>
+      <c r="L42" s="54"/>
     </row>
     <row r="43" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E43" s="58"/>
-      <c r="F43" s="58"/>
-      <c r="G43" s="58"/>
-      <c r="H43" s="58"/>
-      <c r="I43" s="58"/>
-      <c r="J43" s="58"/>
-      <c r="K43" s="58"/>
-      <c r="L43" s="58"/>
+      <c r="E43" s="55"/>
+      <c r="F43" s="55"/>
+      <c r="G43" s="55"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="55"/>
+      <c r="J43" s="55"/>
+      <c r="K43" s="55"/>
+      <c r="L43" s="55"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/aqt_docs.xlsx
+++ b/aqt_docs.xlsx
@@ -9,22 +9,23 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28380" windowHeight="11325" firstSheet="3" activeTab="10"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28380" windowHeight="11325"/>
   </bookViews>
   <sheets>
-    <sheet name="사용법" sheetId="4" r:id="rId1"/>
-    <sheet name="테이블목록" sheetId="1" r:id="rId2"/>
-    <sheet name="작업순서" sheetId="6" r:id="rId3"/>
-    <sheet name="aqt web" sheetId="7" r:id="rId4"/>
-    <sheet name="주요테이블" sheetId="5" r:id="rId5"/>
-    <sheet name="프로그램" sheetId="2" r:id="rId6"/>
-    <sheet name="tcp_http실행구조" sheetId="10" r:id="rId7"/>
-    <sheet name="tmax실행구조" sheetId="8" r:id="rId8"/>
-    <sheet name="기타환경변수" sheetId="3" r:id="rId9"/>
-    <sheet name="Sheet1" sheetId="9" r:id="rId10"/>
-    <sheet name="BC" sheetId="13" r:id="rId11"/>
-    <sheet name="Sheet3" sheetId="11" r:id="rId12"/>
-    <sheet name="Sheet2" sheetId="12" r:id="rId13"/>
+    <sheet name="job" sheetId="14" r:id="rId1"/>
+    <sheet name="사용법" sheetId="4" r:id="rId2"/>
+    <sheet name="테이블목록" sheetId="1" r:id="rId3"/>
+    <sheet name="작업순서" sheetId="6" r:id="rId4"/>
+    <sheet name="aqt web" sheetId="7" r:id="rId5"/>
+    <sheet name="주요테이블" sheetId="5" r:id="rId6"/>
+    <sheet name="프로그램" sheetId="2" r:id="rId7"/>
+    <sheet name="tcp_http실행구조" sheetId="10" r:id="rId8"/>
+    <sheet name="tmax실행구조" sheetId="8" r:id="rId9"/>
+    <sheet name="기타환경변수" sheetId="3" r:id="rId10"/>
+    <sheet name="Sheet1" sheetId="9" r:id="rId11"/>
+    <sheet name="BC" sheetId="13" r:id="rId12"/>
+    <sheet name="우리은행" sheetId="11" r:id="rId13"/>
+    <sheet name="Sheet2" sheetId="12" r:id="rId14"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="532">
   <si>
     <t>tapphosts</t>
   </si>
@@ -2689,10 +2690,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>데이터수집</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>로그수집 및 변환</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3060,6 +3057,102 @@
   </si>
   <si>
     <t>업무의 규모 및 복잡도에 따라 조정됨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트데이터관리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트시 연계시스템 인터페이스 조사, 가상서버검토</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가상서버 커스터마이징</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">가상서버 설치/커스터마이징 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총괄화면 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김대표</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업요청명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>요청자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>요청일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트선행후행 프로그램지정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트 수행전후 수행될 프로그램을 지정하는 기능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AQT에 전문LAYOUT 정의 및 조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전문의 레이아웃을 등록하고 데이터 조회시 레이아웃에 의해 조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방승권</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASW 의 전환현황, 테스트 진행현황 총괄화면 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통합진행table 추가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통합진행 화면 개발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3067,8 +3160,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy&quot;/&quot;mm&quot;/&quot;dd;@"/>
   </numFmts>
   <fonts count="52" x14ac:knownFonts="1">
     <font>
@@ -3466,7 +3560,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3494,6 +3588,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3601,7 +3701,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3788,15 +3888,6 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -3807,15 +3898,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3829,9 +3911,6 @@
     </xf>
     <xf numFmtId="0" fontId="45" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3849,6 +3928,39 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4749,10 +4861,10 @@
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>275602</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>132562</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>166023</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4770,7 +4882,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="781050" y="1581150"/>
-          <a:ext cx="4980952" cy="6304762"/>
+          <a:ext cx="2524125" cy="3194973"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8661,578 +8773,487 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O36"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" style="21"/>
-    <col min="2" max="2" width="42.25" style="21" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="21"/>
+    <col min="1" max="1" width="30.25" customWidth="1"/>
+    <col min="2" max="2" width="20.25" customWidth="1"/>
+    <col min="3" max="3" width="12.75" style="78" customWidth="1"/>
+    <col min="4" max="4" width="60.875" customWidth="1"/>
+    <col min="5" max="5" width="16.875" customWidth="1"/>
+    <col min="7" max="7" width="18.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-    </row>
-    <row r="2" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-    </row>
-    <row r="3" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20"/>
-    </row>
-    <row r="4" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="20"/>
-      <c r="O4" s="20"/>
-    </row>
-    <row r="5" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="28"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-    </row>
-    <row r="6" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="28" t="s">
-        <v>361</v>
-      </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
-      <c r="N6" s="20"/>
-      <c r="O6" s="20"/>
-    </row>
-    <row r="7" spans="1:15" ht="33" x14ac:dyDescent="0.3">
-      <c r="A7" s="28"/>
-      <c r="B7" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="20"/>
-    </row>
-    <row r="8" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="28"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="20"/>
-      <c r="N8" s="20"/>
-      <c r="O8" s="20"/>
-    </row>
-    <row r="9" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-    </row>
-    <row r="10" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="28"/>
-      <c r="B10" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>330</v>
-      </c>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="28"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="20"/>
-    </row>
-    <row r="11" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="28"/>
-      <c r="B11" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="C11" s="28" t="s">
-        <v>331</v>
-      </c>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="28"/>
-      <c r="K11" s="20"/>
-      <c r="L11" s="20"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="20"/>
-    </row>
-    <row r="12" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="28"/>
-      <c r="B12" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>332</v>
-      </c>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
-      <c r="M12" s="20"/>
-      <c r="N12" s="20"/>
-      <c r="O12" s="20"/>
-    </row>
-    <row r="13" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="28"/>
-      <c r="B13" s="28" t="s">
-        <v>357</v>
-      </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="20"/>
-      <c r="M13" s="20"/>
-      <c r="N13" s="20"/>
-      <c r="O13" s="20"/>
-    </row>
-    <row r="14" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A14" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="28"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
-      <c r="M14" s="20"/>
-      <c r="N14" s="20"/>
-      <c r="O14" s="20"/>
-    </row>
-    <row r="15" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="28"/>
-      <c r="B15" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="20"/>
-    </row>
-    <row r="16" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A16" s="28"/>
-      <c r="B16" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="20"/>
-    </row>
-    <row r="17" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A17" s="28"/>
-      <c r="B17" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="20"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="20"/>
-    </row>
-    <row r="18" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="28"/>
-      <c r="B18" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-      <c r="M18" s="20"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="20"/>
-    </row>
-    <row r="19" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="28"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="20"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="20"/>
-    </row>
-    <row r="20" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A20" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-      <c r="M20" s="20"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="20"/>
-    </row>
-    <row r="21" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A21" s="28"/>
-      <c r="B21" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="28"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="20"/>
-    </row>
-    <row r="22" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A22" s="28"/>
-      <c r="B22" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20"/>
-    </row>
-    <row r="23" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A23" s="28"/>
-      <c r="B23" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="C23" s="31"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20"/>
-    </row>
-    <row r="24" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A24" s="28"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="31" t="s">
-        <v>349</v>
-      </c>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20"/>
-    </row>
-    <row r="25" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A25" s="28"/>
-      <c r="B25" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="C25" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20"/>
-    </row>
-    <row r="26" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A26" s="28"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="20"/>
-    </row>
-    <row r="27" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A27" s="28"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
-      <c r="M27" s="20"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="20"/>
-    </row>
-    <row r="28" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A28" s="28"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="20"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B29" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="21" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="B33" s="27" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="B34" s="27" t="s">
-        <v>353</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="B35" s="27" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="B36" s="27" t="s">
-        <v>355</v>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="76" t="s">
+        <v>514</v>
+      </c>
+      <c r="B1" s="76" t="s">
+        <v>515</v>
+      </c>
+      <c r="C1" s="77" t="s">
+        <v>516</v>
+      </c>
+      <c r="D1" s="76" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="76" t="s">
+        <v>517</v>
+      </c>
+      <c r="F1" s="76" t="s">
+        <v>521</v>
+      </c>
+      <c r="G1" s="76" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C2" s="78">
+        <v>45962</v>
+      </c>
+      <c r="D2" t="s">
+        <v>524</v>
+      </c>
+      <c r="E2" s="79">
+        <v>0.9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>518</v>
+      </c>
+      <c r="B3" t="s">
+        <v>519</v>
+      </c>
+      <c r="C3" s="78">
+        <v>46114</v>
+      </c>
+      <c r="D3" t="s">
+        <v>520</v>
+      </c>
+      <c r="F3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>512</v>
+      </c>
+      <c r="B4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C4" s="78">
+        <v>46149</v>
+      </c>
+      <c r="D4" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C5" s="78">
+        <v>46153</v>
+      </c>
+      <c r="D5" t="s">
+        <v>528</v>
+      </c>
+      <c r="F5" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C6" s="78">
+        <v>46153</v>
+      </c>
+      <c r="D6" t="s">
+        <v>530</v>
+      </c>
+      <c r="F6" t="s">
+        <v>531</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B62"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="41.375" customWidth="1"/>
+    <col min="2" max="2" width="12.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="B9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>233</v>
+      </c>
+      <c r="B10" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A11" s="39" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A12" s="4"/>
+    </row>
+    <row r="13" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="37" t="s">
+        <v>390</v>
+      </c>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="37" t="s">
+        <v>371</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="37" t="s">
+        <v>378</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="37" t="s">
+        <v>372</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="37" t="s">
+        <v>382</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="37" t="s">
+        <v>374</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="37" t="s">
+        <v>367</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="37" t="s">
+        <v>368</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="37" t="s">
+        <v>386</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="37" t="s">
+        <v>376</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="37" t="s">
+        <v>370</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="37" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="37"/>
+    </row>
+    <row r="30" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" s="1"/>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" s="6" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" s="24" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" s="24" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" s="25"/>
+    </row>
+    <row r="59" spans="1:1" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A59" s="26" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="33" x14ac:dyDescent="0.3">
+      <c r="A60" s="26" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" s="24" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" s="24" t="s">
+        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -9242,7 +9263,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -9268,83 +9289,83 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.75" style="51" customWidth="1"/>
     <col min="2" max="2" width="30.125" style="51" customWidth="1"/>
-    <col min="3" max="3" width="46.375" style="78" customWidth="1"/>
+    <col min="3" max="3" width="46.375" style="71" customWidth="1"/>
     <col min="4" max="4" width="11.875" style="51" customWidth="1"/>
     <col min="5" max="9" width="6.375" style="51" customWidth="1"/>
     <col min="10" max="16384" width="9" style="51"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="80" t="s">
+        <v>435</v>
+      </c>
+      <c r="B1" s="80" t="s">
         <v>436</v>
       </c>
-      <c r="B1" s="69" t="s">
+      <c r="C1" s="81" t="s">
         <v>437</v>
       </c>
-      <c r="C1" s="76" t="s">
-        <v>438</v>
-      </c>
-      <c r="D1" s="70" t="s">
-        <v>441</v>
-      </c>
-      <c r="E1" s="69" t="s">
-        <v>435</v>
-      </c>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69" t="s">
+      <c r="D1" s="82" t="s">
+        <v>440</v>
+      </c>
+      <c r="E1" s="80" t="s">
         <v>434</v>
       </c>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80" t="s">
+        <v>433</v>
+      </c>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
     </row>
     <row r="2" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="69"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="72" t="s">
+      <c r="A2" s="80"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="66" t="s">
+        <v>427</v>
+      </c>
+      <c r="F2" s="66" t="s">
         <v>428</v>
       </c>
-      <c r="F2" s="72" t="s">
+      <c r="G2" s="66" t="s">
         <v>429</v>
       </c>
-      <c r="G2" s="72" t="s">
+      <c r="H2" s="66" t="s">
         <v>430</v>
       </c>
-      <c r="H2" s="72" t="s">
+      <c r="I2" s="66" t="s">
         <v>431</v>
       </c>
-      <c r="I2" s="72" t="s">
-        <v>432</v>
-      </c>
-      <c r="J2" s="69"/>
+      <c r="J2" s="80"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="67" t="s">
         <v>403</v>
       </c>
-      <c r="B3" s="73"/>
+      <c r="B3" s="67"/>
       <c r="C3" s="52"/>
       <c r="D3" s="49"/>
       <c r="E3" s="49">
         <v>2</v>
       </c>
       <c r="F3" s="49"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="73"/>
-      <c r="B4" s="73" t="s">
+      <c r="A4" s="67"/>
+      <c r="B4" s="67" t="s">
         <v>404</v>
       </c>
       <c r="C4" s="52" t="s">
@@ -9353,13 +9374,13 @@
       <c r="D4" s="49"/>
       <c r="E4" s="49"/>
       <c r="F4" s="49"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="73"/>
-      <c r="B5" s="73" t="s">
+      <c r="A5" s="67"/>
+      <c r="B5" s="67" t="s">
         <v>405</v>
       </c>
       <c r="C5" s="52" t="s">
@@ -9368,43 +9389,43 @@
       <c r="D5" s="49"/>
       <c r="E5" s="49"/>
       <c r="F5" s="49"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="67" t="s">
         <v>407</v>
       </c>
-      <c r="B6" s="73"/>
+      <c r="B6" s="67"/>
       <c r="C6" s="52"/>
       <c r="D6" s="49"/>
       <c r="E6" s="49"/>
       <c r="F6" s="49">
         <v>2</v>
       </c>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
+      <c r="G6" s="74"/>
+      <c r="H6" s="74"/>
+      <c r="I6" s="74"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="73"/>
-      <c r="B7" s="73" t="s">
-        <v>444</v>
+      <c r="A7" s="67"/>
+      <c r="B7" s="67" t="s">
+        <v>443</v>
       </c>
       <c r="C7" s="52"/>
       <c r="D7" s="49" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E7" s="49"/>
       <c r="F7" s="49"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
+      <c r="G7" s="74"/>
+      <c r="H7" s="74"/>
+      <c r="I7" s="74"/>
     </row>
     <row r="8" spans="1:10" ht="66" x14ac:dyDescent="0.3">
-      <c r="A8" s="73"/>
-      <c r="B8" s="73" t="s">
+      <c r="A8" s="67"/>
+      <c r="B8" s="67" t="s">
         <v>414</v>
       </c>
       <c r="C8" s="52" t="s">
@@ -9413,13 +9434,13 @@
       <c r="D8" s="53"/>
       <c r="E8" s="49"/>
       <c r="F8" s="49"/>
-      <c r="G8" s="81"/>
-      <c r="H8" s="81"/>
-      <c r="I8" s="81"/>
+      <c r="G8" s="74"/>
+      <c r="H8" s="74"/>
+      <c r="I8" s="74"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="73"/>
-      <c r="B9" s="73" t="s">
+      <c r="A9" s="67"/>
+      <c r="B9" s="67" t="s">
         <v>415</v>
       </c>
       <c r="C9" s="52" t="s">
@@ -9428,184 +9449,184 @@
       <c r="D9" s="53"/>
       <c r="E9" s="49"/>
       <c r="F9" s="49"/>
-      <c r="G9" s="81"/>
-      <c r="H9" s="81"/>
-      <c r="I9" s="81"/>
+      <c r="G9" s="74"/>
+      <c r="H9" s="74"/>
+      <c r="I9" s="74"/>
     </row>
     <row r="10" spans="1:10" ht="66" x14ac:dyDescent="0.3">
-      <c r="A10" s="73"/>
-      <c r="B10" s="73" t="s">
+      <c r="A10" s="67"/>
+      <c r="B10" s="67" t="s">
         <v>408</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D10" s="53"/>
       <c r="E10" s="49"/>
       <c r="F10" s="49"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="81"/>
+      <c r="G10" s="74"/>
+      <c r="H10" s="74"/>
+      <c r="I10" s="74"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="73" t="s">
-        <v>494</v>
-      </c>
-      <c r="B11" s="73"/>
+      <c r="A11" s="67" t="s">
+        <v>493</v>
+      </c>
+      <c r="B11" s="67"/>
       <c r="C11" s="52"/>
       <c r="D11" s="49"/>
       <c r="E11" s="49"/>
       <c r="F11" s="49">
         <v>1</v>
       </c>
-      <c r="G11" s="81">
+      <c r="G11" s="74">
         <v>1</v>
       </c>
-      <c r="H11" s="81">
+      <c r="H11" s="74">
         <v>1</v>
       </c>
-      <c r="I11" s="81">
+      <c r="I11" s="74">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="33" x14ac:dyDescent="0.3">
-      <c r="A12" s="73"/>
-      <c r="B12" s="73" t="s">
+      <c r="A12" s="67"/>
+      <c r="B12" s="67" t="s">
+        <v>417</v>
+      </c>
+      <c r="C12" s="52" t="s">
         <v>418</v>
-      </c>
-      <c r="C12" s="52" t="s">
-        <v>419</v>
       </c>
       <c r="D12" s="53"/>
       <c r="E12" s="49"/>
       <c r="F12" s="49"/>
-      <c r="G12" s="81"/>
-      <c r="H12" s="81"/>
-      <c r="I12" s="81"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="74"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="73"/>
-      <c r="B13" s="73" t="s">
-        <v>493</v>
+      <c r="A13" s="67"/>
+      <c r="B13" s="67" t="s">
+        <v>492</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D13" s="53" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E13" s="49"/>
       <c r="F13" s="49"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="81"/>
-      <c r="I13" s="81"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
     </row>
     <row r="14" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="73"/>
-      <c r="B14" s="73" t="s">
+      <c r="A14" s="67"/>
+      <c r="B14" s="67" t="s">
+        <v>419</v>
+      </c>
+      <c r="C14" s="52" t="s">
         <v>420</v>
       </c>
-      <c r="C14" s="52" t="s">
-        <v>421</v>
-      </c>
       <c r="D14" s="53" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E14" s="49"/>
       <c r="F14" s="49"/>
-      <c r="G14" s="81"/>
-      <c r="H14" s="81"/>
-      <c r="I14" s="81"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="74"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="73" t="s">
-        <v>500</v>
-      </c>
-      <c r="B15" s="73"/>
+      <c r="A15" s="67" t="s">
+        <v>499</v>
+      </c>
+      <c r="B15" s="67"/>
       <c r="C15" s="52"/>
       <c r="D15" s="49"/>
       <c r="E15" s="49"/>
       <c r="F15" s="49"/>
-      <c r="G15" s="81"/>
-      <c r="H15" s="81"/>
-      <c r="I15" s="81"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="74"/>
+      <c r="I15" s="74"/>
     </row>
     <row r="16" spans="1:10" ht="33" x14ac:dyDescent="0.3">
-      <c r="A16" s="73"/>
-      <c r="B16" s="73" t="s">
-        <v>422</v>
+      <c r="A16" s="67"/>
+      <c r="B16" s="67" t="s">
+        <v>421</v>
       </c>
       <c r="C16" s="52" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D16" s="53"/>
       <c r="E16" s="49"/>
       <c r="F16" s="49"/>
-      <c r="G16" s="81">
+      <c r="G16" s="74">
         <v>1</v>
       </c>
-      <c r="H16" s="81">
+      <c r="H16" s="74">
         <v>1</v>
       </c>
-      <c r="I16" s="81"/>
+      <c r="I16" s="74"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="73"/>
-      <c r="B17" s="73" t="s">
+      <c r="A17" s="67"/>
+      <c r="B17" s="67" t="s">
+        <v>495</v>
+      </c>
+      <c r="C17" s="52" t="s">
         <v>496</v>
-      </c>
-      <c r="C17" s="52" t="s">
-        <v>497</v>
       </c>
       <c r="D17" s="53"/>
       <c r="E17" s="49"/>
       <c r="F17" s="49"/>
-      <c r="G17" s="81">
+      <c r="G17" s="74">
         <v>1</v>
       </c>
-      <c r="H17" s="81">
+      <c r="H17" s="74">
         <v>1</v>
       </c>
-      <c r="I17" s="81">
+      <c r="I17" s="74">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="73"/>
-      <c r="B18" s="65" t="s">
-        <v>498</v>
-      </c>
-      <c r="C18" s="66" t="s">
-        <v>426</v>
-      </c>
-      <c r="D18" s="67" t="s">
+      <c r="A18" s="67"/>
+      <c r="B18" s="62" t="s">
+        <v>497</v>
+      </c>
+      <c r="C18" s="63" t="s">
+        <v>425</v>
+      </c>
+      <c r="D18" s="64" t="s">
+        <v>441</v>
+      </c>
+      <c r="E18" s="65"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="75"/>
+      <c r="H18" s="75"/>
+      <c r="I18" s="75"/>
+      <c r="J18" s="72" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="67" t="s">
         <v>442</v>
       </c>
-      <c r="E18" s="68"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="82"/>
-      <c r="H18" s="82"/>
-      <c r="I18" s="82"/>
-      <c r="J18" s="79" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="73" t="s">
-        <v>443</v>
-      </c>
-      <c r="B19" s="73"/>
+      <c r="B19" s="67"/>
       <c r="C19" s="52"/>
       <c r="D19" s="49"/>
       <c r="E19" s="49"/>
       <c r="F19" s="49"/>
-      <c r="G19" s="81"/>
-      <c r="H19" s="81"/>
-      <c r="I19" s="81"/>
+      <c r="G19" s="74"/>
+      <c r="H19" s="74"/>
+      <c r="I19" s="74"/>
     </row>
     <row r="20" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A20" s="73"/>
-      <c r="B20" s="73" t="s">
+      <c r="A20" s="67"/>
+      <c r="B20" s="67" t="s">
         <v>409</v>
       </c>
       <c r="C20" s="52" t="s">
@@ -9616,75 +9637,75 @@
       <c r="F20" s="49">
         <v>1</v>
       </c>
-      <c r="G20" s="81"/>
-      <c r="H20" s="81"/>
-      <c r="I20" s="81"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="74"/>
     </row>
     <row r="21" spans="1:10" ht="33" x14ac:dyDescent="0.3">
-      <c r="A21" s="73"/>
-      <c r="B21" s="73" t="s">
+      <c r="A21" s="67"/>
+      <c r="B21" s="67" t="s">
+        <v>422</v>
+      </c>
+      <c r="C21" s="52" t="s">
         <v>423</v>
-      </c>
-      <c r="C21" s="52" t="s">
-        <v>424</v>
       </c>
       <c r="D21" s="53"/>
       <c r="E21" s="49"/>
       <c r="F21" s="49"/>
-      <c r="G21" s="81">
+      <c r="G21" s="74">
         <v>1</v>
       </c>
-      <c r="H21" s="81">
+      <c r="H21" s="74">
         <v>1</v>
       </c>
-      <c r="I21" s="81">
+      <c r="I21" s="74">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="73"/>
-      <c r="B22" s="65" t="s">
+      <c r="A22" s="67"/>
+      <c r="B22" s="62" t="s">
+        <v>424</v>
+      </c>
+      <c r="C22" s="63" t="s">
         <v>425</v>
       </c>
-      <c r="C22" s="66" t="s">
-        <v>426</v>
-      </c>
-      <c r="D22" s="67" t="s">
-        <v>442</v>
-      </c>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="82"/>
-      <c r="H22" s="82"/>
-      <c r="I22" s="82"/>
-      <c r="J22" s="79" t="s">
-        <v>508</v>
+      <c r="D22" s="64" t="s">
+        <v>441</v>
+      </c>
+      <c r="E22" s="65"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="75"/>
+      <c r="H22" s="75"/>
+      <c r="I22" s="75"/>
+      <c r="J22" s="72" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="74" t="s">
-        <v>439</v>
-      </c>
-      <c r="B23" s="75"/>
-      <c r="C23" s="77"/>
-      <c r="D23" s="75"/>
-      <c r="E23" s="72">
+      <c r="A23" s="68" t="s">
+        <v>438</v>
+      </c>
+      <c r="B23" s="69"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="66">
         <f t="shared" ref="E23:F23" si="0">SUM(E3:E21)</f>
         <v>2</v>
       </c>
-      <c r="F23" s="72">
+      <c r="F23" s="66">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G23" s="72">
+      <c r="G23" s="66">
         <f>SUM(G3:G22)</f>
         <v>4</v>
       </c>
-      <c r="H23" s="72">
+      <c r="H23" s="66">
         <f>SUM(H3:H22)</f>
         <v>4</v>
       </c>
-      <c r="I23" s="72">
+      <c r="I23" s="66">
         <f>SUM(I3:I22)</f>
         <v>3</v>
       </c>
@@ -9695,65 +9716,65 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C25" s="51" t="s">
-        <v>501</v>
-      </c>
-      <c r="D25" s="80">
+        <v>500</v>
+      </c>
+      <c r="D25" s="73">
         <f>1687+5809+7451</f>
         <v>14947</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C26" s="78" t="s">
+      <c r="C26" s="71" t="s">
+        <v>501</v>
+      </c>
+      <c r="D26" s="73">
+        <v>8404</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D27" s="73"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C28" s="71" t="s">
         <v>502</v>
       </c>
-      <c r="D26" s="80">
-        <v>8404</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D27" s="80"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C28" s="78" t="s">
-        <v>503</v>
-      </c>
-      <c r="D28" s="80">
+      <c r="D28" s="73">
         <f>6544+613+1421</f>
         <v>8578</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C29" s="78" t="s">
+      <c r="C29" s="71" t="s">
+        <v>503</v>
+      </c>
+      <c r="D29" s="73">
+        <v>5511</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D30" s="73"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="71" t="s">
         <v>504</v>
       </c>
-      <c r="D29" s="80">
-        <v>5511</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D30" s="80"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C31" s="78" t="s">
-        <v>505</v>
-      </c>
-      <c r="D31" s="80">
+      <c r="D31" s="73">
         <f>31438+32761</f>
         <v>64199</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="78" t="s">
-        <v>506</v>
-      </c>
-      <c r="D32" s="80">
+      <c r="C32" s="71" t="s">
+        <v>505</v>
+      </c>
+      <c r="D32" s="73">
         <f>20244+30315</f>
         <v>50559</v>
       </c>
     </row>
     <row r="34" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C34" s="78" t="s">
-        <v>507</v>
+      <c r="C34" s="71" t="s">
+        <v>506</v>
       </c>
     </row>
   </sheetData>
@@ -9772,9 +9793,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.125" customWidth="1"/>
@@ -9785,51 +9806,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="84" t="s">
+        <v>435</v>
+      </c>
+      <c r="B1" s="84" t="s">
         <v>436</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="C1" s="84" t="s">
         <v>437</v>
       </c>
-      <c r="C1" s="62" t="s">
-        <v>438</v>
-      </c>
-      <c r="D1" s="63" t="s">
-        <v>441</v>
-      </c>
-      <c r="E1" s="62" t="s">
-        <v>435</v>
-      </c>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62" t="s">
+      <c r="D1" s="85" t="s">
+        <v>440</v>
+      </c>
+      <c r="E1" s="84" t="s">
         <v>434</v>
       </c>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84" t="s">
+        <v>433</v>
+      </c>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="84"/>
     </row>
     <row r="2" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="62"/>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="64"/>
+      <c r="A2" s="84"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="86"/>
       <c r="E2" s="47" t="s">
+        <v>427</v>
+      </c>
+      <c r="F2" s="47" t="s">
         <v>428</v>
       </c>
-      <c r="F2" s="47" t="s">
+      <c r="G2" s="47" t="s">
         <v>429</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="H2" s="47" t="s">
         <v>430</v>
       </c>
-      <c r="H2" s="47" t="s">
+      <c r="I2" s="47" t="s">
         <v>431</v>
       </c>
-      <c r="I2" s="47" t="s">
+      <c r="J2" s="47" t="s">
         <v>432</v>
-      </c>
-      <c r="J2" s="47" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -9870,7 +9891,7 @@
         <v>405</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>406</v>
+        <v>509</v>
       </c>
       <c r="D5" s="40"/>
       <c r="E5" s="40"/>
@@ -9899,11 +9920,11 @@
     <row r="7" spans="1:10" s="51" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="48"/>
       <c r="B7" s="48" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C7" s="48"/>
       <c r="D7" s="49" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E7" s="49"/>
       <c r="F7" s="49"/>
@@ -9944,13 +9965,13 @@
       <c r="I9" s="41"/>
       <c r="J9" s="41"/>
     </row>
-    <row r="10" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="42"/>
       <c r="B10" s="42" t="s">
-        <v>408</v>
+        <v>510</v>
       </c>
       <c r="C10" s="43" t="s">
-        <v>411</v>
+        <v>511</v>
       </c>
       <c r="D10" s="44"/>
       <c r="E10" s="40"/>
@@ -9962,7 +9983,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="42" t="s">
-        <v>417</v>
+        <v>508</v>
       </c>
       <c r="B11" s="42"/>
       <c r="C11" s="42"/>
@@ -9982,13 +10003,13 @@
       </c>
       <c r="J11" s="41"/>
     </row>
-    <row r="12" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A12" s="42"/>
       <c r="B12" s="42" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="C12" s="43" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="D12" s="44"/>
       <c r="E12" s="40"/>
@@ -9998,17 +10019,15 @@
       <c r="I12" s="41"/>
       <c r="J12" s="41"/>
     </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A13" s="42"/>
       <c r="B13" s="42" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C13" s="43" t="s">
-        <v>421</v>
-      </c>
-      <c r="D13" s="44" t="s">
-        <v>442</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="D13" s="44"/>
       <c r="E13" s="40"/>
       <c r="F13" s="40"/>
       <c r="G13" s="41"/>
@@ -10016,13 +10035,17 @@
       <c r="I13" s="41"/>
       <c r="J13" s="41"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="42" t="s">
-        <v>491</v>
-      </c>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="40"/>
+    <row r="14" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="42"/>
+      <c r="B14" s="42" t="s">
+        <v>419</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>420</v>
+      </c>
+      <c r="D14" s="44" t="s">
+        <v>441</v>
+      </c>
       <c r="E14" s="40"/>
       <c r="F14" s="40"/>
       <c r="G14" s="41"/>
@@ -10030,95 +10053,93 @@
       <c r="I14" s="41"/>
       <c r="J14" s="41"/>
     </row>
-    <row r="15" spans="1:10" ht="33" x14ac:dyDescent="0.3">
-      <c r="A15" s="42"/>
-      <c r="B15" s="42" t="s">
-        <v>422</v>
-      </c>
-      <c r="C15" s="43" t="s">
-        <v>427</v>
-      </c>
-      <c r="D15" s="44"/>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="42" t="s">
+        <v>490</v>
+      </c>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="40"/>
       <c r="E15" s="40"/>
       <c r="F15" s="40"/>
-      <c r="G15" s="41">
-        <v>1</v>
-      </c>
-      <c r="H15" s="41">
-        <v>1</v>
-      </c>
-      <c r="I15" s="41">
-        <v>1</v>
-      </c>
-      <c r="J15" s="41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+    </row>
+    <row r="16" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A16" s="42"/>
       <c r="B16" s="42" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C16" s="43" t="s">
         <v>426</v>
       </c>
-      <c r="D16" s="44" t="s">
-        <v>442</v>
-      </c>
+      <c r="D16" s="44"/>
       <c r="E16" s="40"/>
       <c r="F16" s="40"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
+      <c r="G16" s="41">
+        <v>1</v>
+      </c>
+      <c r="H16" s="41">
+        <v>1</v>
+      </c>
+      <c r="I16" s="41">
+        <v>1</v>
+      </c>
+      <c r="J16" s="41">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="42" t="s">
-        <v>443</v>
-      </c>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="40"/>
+      <c r="A17" s="42"/>
+      <c r="B17" s="42" t="s">
+        <v>424</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>425</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>441</v>
+      </c>
       <c r="E17" s="40"/>
-      <c r="F17" s="40">
+      <c r="F17" s="40"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40">
         <v>1</v>
       </c>
-      <c r="G17" s="41">
+      <c r="G18" s="41">
         <v>2</v>
       </c>
-      <c r="H17" s="41">
+      <c r="H18" s="41">
         <v>2</v>
       </c>
-      <c r="I17" s="41">
+      <c r="I18" s="41">
         <v>2</v>
       </c>
-      <c r="J17" s="41">
+      <c r="J18" s="41">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="42"/>
-      <c r="B18" s="42" t="s">
-        <v>409</v>
-      </c>
-      <c r="C18" s="43" t="s">
-        <v>410</v>
-      </c>
-      <c r="D18" s="44"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="41"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A19" s="42"/>
       <c r="B19" s="42" t="s">
-        <v>423</v>
+        <v>409</v>
       </c>
       <c r="C19" s="43" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="D19" s="44"/>
       <c r="E19" s="40"/>
@@ -10131,14 +10152,12 @@
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="42"/>
       <c r="B20" s="42" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C20" s="43" t="s">
-        <v>426</v>
-      </c>
-      <c r="D20" s="44" t="s">
-        <v>442</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="D20" s="44"/>
       <c r="E20" s="40"/>
       <c r="F20" s="40"/>
       <c r="G20" s="41"/>
@@ -10147,33 +10166,51 @@
       <c r="J20" s="41"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="46" t="s">
-        <v>439</v>
-      </c>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="47">
-        <f t="shared" ref="E21:J21" si="0">SUM(E3:E19)</f>
+      <c r="A21" s="42"/>
+      <c r="B21" s="42" t="s">
+        <v>424</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>425</v>
+      </c>
+      <c r="D21" s="44" t="s">
+        <v>441</v>
+      </c>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="41"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="46" t="s">
+        <v>438</v>
+      </c>
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="47">
+        <f t="shared" ref="E22:J22" si="0">SUM(E3:E20)</f>
         <v>1</v>
       </c>
-      <c r="F21" s="47">
+      <c r="F22" s="47">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G21" s="47">
+      <c r="G22" s="47">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H21" s="47">
+      <c r="H22" s="47">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I21" s="47">
+      <c r="I22" s="47">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="J21" s="47">
+      <c r="J22" s="47">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -10193,7 +10230,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M43"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -10213,62 +10250,62 @@
   <sheetData>
     <row r="1" spans="1:13" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E1" s="61" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">
+        <v>444</v>
+      </c>
+      <c r="B2" s="56" t="s">
         <v>445</v>
       </c>
-      <c r="B2" s="56" t="s">
+      <c r="C2" s="56" t="s">
+        <v>473</v>
+      </c>
+      <c r="D2" s="56" t="s">
+        <v>453</v>
+      </c>
+      <c r="E2" s="56" t="s">
         <v>446</v>
       </c>
-      <c r="C2" s="56" t="s">
-        <v>474</v>
-      </c>
-      <c r="D2" s="56" t="s">
-        <v>454</v>
-      </c>
-      <c r="E2" s="56" t="s">
+      <c r="F2" s="56" t="s">
         <v>447</v>
       </c>
-      <c r="F2" s="56" t="s">
+      <c r="G2" s="56" t="s">
+        <v>449</v>
+      </c>
+      <c r="H2" s="56" t="s">
         <v>448</v>
       </c>
-      <c r="G2" s="56" t="s">
+      <c r="I2" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="J2" s="56" t="s">
         <v>450</v>
       </c>
-      <c r="H2" s="56" t="s">
-        <v>449</v>
-      </c>
-      <c r="I2" s="56" t="s">
-        <v>478</v>
-      </c>
-      <c r="J2" s="56" t="s">
+      <c r="K2" s="56" t="s">
         <v>451</v>
       </c>
-      <c r="K2" s="56" t="s">
+      <c r="L2" s="56" t="s">
         <v>452</v>
       </c>
-      <c r="L2" s="56" t="s">
-        <v>453</v>
-      </c>
       <c r="M2" s="56" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="57" t="s">
+        <v>454</v>
+      </c>
+      <c r="B3" s="58" t="s">
         <v>455</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="C3" s="58" t="s">
+        <v>474</v>
+      </c>
+      <c r="D3" s="58" t="s">
         <v>456</v>
-      </c>
-      <c r="C3" s="58" t="s">
-        <v>475</v>
-      </c>
-      <c r="D3" s="58" t="s">
-        <v>457</v>
       </c>
       <c r="E3" s="59">
         <v>46082</v>
@@ -10281,19 +10318,19 @@
         <v>46084</v>
       </c>
       <c r="I3" s="59" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J3" s="59">
         <v>46085</v>
       </c>
       <c r="K3" s="57" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L3" s="59">
         <v>46086</v>
       </c>
       <c r="M3" s="58" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -10308,7 +10345,7 @@
       <c r="I4" s="59"/>
       <c r="J4" s="59"/>
       <c r="K4" s="57" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="L4" s="59"/>
       <c r="M4" s="58"/>
@@ -10325,7 +10362,7 @@
       <c r="I5" s="59"/>
       <c r="J5" s="59"/>
       <c r="K5" s="57" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L5" s="59"/>
       <c r="M5" s="58"/>
@@ -10342,13 +10379,13 @@
       <c r="I6" s="59"/>
       <c r="J6" s="59"/>
       <c r="K6" s="57" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L6" s="59">
         <v>46086</v>
       </c>
       <c r="M6" s="58" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -10367,11 +10404,11 @@
         <v>46092</v>
       </c>
       <c r="I7" s="59" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J7" s="59"/>
       <c r="K7" s="57" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L7" s="59"/>
       <c r="M7" s="58"/>
@@ -10388,7 +10425,7 @@
       <c r="I8" s="59"/>
       <c r="J8" s="59"/>
       <c r="K8" s="57" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="L8" s="59"/>
       <c r="M8" s="58"/>
@@ -10405,7 +10442,7 @@
       <c r="I9" s="59"/>
       <c r="J9" s="59"/>
       <c r="K9" s="57" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L9" s="59"/>
       <c r="M9" s="58"/>
@@ -10422,22 +10459,22 @@
       <c r="I10" s="59"/>
       <c r="J10" s="59"/>
       <c r="K10" s="57" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L10" s="59"/>
       <c r="M10" s="58" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="57" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C11" s="58" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D11" s="58"/>
       <c r="E11" s="59">
@@ -10451,19 +10488,19 @@
         <v>46084</v>
       </c>
       <c r="I11" s="59" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J11" s="59">
         <v>46085</v>
       </c>
       <c r="K11" s="57" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L11" s="59">
         <v>46086</v>
       </c>
       <c r="M11" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -10478,7 +10515,7 @@
       <c r="I12" s="59"/>
       <c r="J12" s="59"/>
       <c r="K12" s="57" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="L12" s="59"/>
       <c r="M12" s="58"/>
@@ -10495,13 +10532,13 @@
       <c r="I13" s="59"/>
       <c r="J13" s="59"/>
       <c r="K13" s="57" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L13" s="59">
         <v>46086</v>
       </c>
       <c r="M13" s="58" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
@@ -10520,11 +10557,11 @@
         <v>46092</v>
       </c>
       <c r="I14" s="59" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J14" s="59"/>
       <c r="K14" s="57" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L14" s="59"/>
       <c r="M14" s="58"/>
@@ -10541,7 +10578,7 @@
       <c r="I15" s="59"/>
       <c r="J15" s="59"/>
       <c r="K15" s="57" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="L15" s="59"/>
       <c r="M15" s="58"/>
@@ -10558,7 +10595,7 @@
       <c r="I16" s="59"/>
       <c r="J16" s="59"/>
       <c r="K16" s="57" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L16" s="59"/>
       <c r="M16" s="58"/>
@@ -10575,25 +10612,25 @@
       <c r="I17" s="59"/>
       <c r="J17" s="59"/>
       <c r="K17" s="57" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L17" s="59"/>
       <c r="M17" s="58" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="57" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B18" s="60" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E18" s="59">
         <v>46082</v>
@@ -10606,19 +10643,19 @@
         <v>46084</v>
       </c>
       <c r="I18" s="59" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="J18" s="59">
         <v>46085</v>
       </c>
       <c r="K18" s="57" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L18" s="59">
         <v>46086</v>
       </c>
       <c r="M18" s="58" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
@@ -10630,7 +10667,7 @@
         <v>46090</v>
       </c>
       <c r="F19" s="57" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G19" s="59"/>
       <c r="H19" s="59"/>
@@ -10642,16 +10679,16 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="57" t="s">
+        <v>481</v>
+      </c>
+      <c r="B20" s="58" t="s">
         <v>482</v>
       </c>
-      <c r="B20" s="58" t="s">
+      <c r="C20" s="58" t="s">
         <v>483</v>
       </c>
-      <c r="C20" s="58" t="s">
+      <c r="D20" s="58" t="s">
         <v>484</v>
-      </c>
-      <c r="D20" s="58" t="s">
-        <v>485</v>
       </c>
       <c r="E20" s="59">
         <v>46083</v>
@@ -10664,19 +10701,19 @@
         <v>46092</v>
       </c>
       <c r="I20" s="59" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="J20" s="59">
         <v>46092</v>
       </c>
       <c r="K20" s="57" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="L20" s="59">
         <v>46092</v>
       </c>
       <c r="M20" s="58" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
@@ -10963,6 +11000,589 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O36"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="21"/>
+    <col min="2" max="2" width="42.25" style="21" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+    </row>
+    <row r="2" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="28"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+    </row>
+    <row r="3" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+    </row>
+    <row r="4" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="28"/>
+      <c r="B4" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+    </row>
+    <row r="5" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="28"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+    </row>
+    <row r="6" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="28" t="s">
+        <v>361</v>
+      </c>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+    </row>
+    <row r="7" spans="1:15" ht="33" x14ac:dyDescent="0.3">
+      <c r="A7" s="28"/>
+      <c r="B7" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+    </row>
+    <row r="8" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="28"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+    </row>
+    <row r="9" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+    </row>
+    <row r="10" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="28"/>
+      <c r="B10" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>330</v>
+      </c>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+    </row>
+    <row r="11" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="28"/>
+      <c r="B11" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>331</v>
+      </c>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+    </row>
+    <row r="12" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="28"/>
+      <c r="B12" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>332</v>
+      </c>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+    </row>
+    <row r="13" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="28"/>
+      <c r="B13" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+    </row>
+    <row r="14" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+    </row>
+    <row r="15" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="28"/>
+      <c r="B15" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+    </row>
+    <row r="16" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A16" s="28"/>
+      <c r="B16" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+    </row>
+    <row r="17" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A17" s="28"/>
+      <c r="B17" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+    </row>
+    <row r="18" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A18" s="28"/>
+      <c r="B18" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+    </row>
+    <row r="19" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A19" s="28"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+    </row>
+    <row r="20" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+    </row>
+    <row r="21" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A21" s="28"/>
+      <c r="B21" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+    </row>
+    <row r="22" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A22" s="28"/>
+      <c r="B22" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+    </row>
+    <row r="23" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A23" s="28"/>
+      <c r="B23" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C23" s="31"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+    </row>
+    <row r="24" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A24" s="28"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="31" t="s">
+        <v>349</v>
+      </c>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+    </row>
+    <row r="25" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A25" s="28"/>
+      <c r="B25" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+    </row>
+    <row r="26" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A26" s="28"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+    </row>
+    <row r="27" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A27" s="28"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+    </row>
+    <row r="28" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A28" s="28"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B29" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="21" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="B33" s="27" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="B34" s="27" t="s">
+        <v>353</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="B35" s="27" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="B36" s="27" t="s">
+        <v>355</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11105,7 +11725,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
@@ -11220,7 +11840,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -11257,7 +11877,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:C87"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -12131,7 +12751,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -12508,17 +13128,6 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -12535,379 +13144,11 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="41.375" customWidth="1"/>
-    <col min="2" max="2" width="12.125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="B7" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="B9" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>233</v>
-      </c>
-      <c r="B10" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A11" s="39" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A12" s="4"/>
-    </row>
-    <row r="13" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="37" t="s">
-        <v>390</v>
-      </c>
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="37" t="s">
-        <v>371</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="37" t="s">
-        <v>378</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="37" t="s">
-        <v>375</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="37" t="s">
-        <v>372</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="37" t="s">
-        <v>382</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="37" t="s">
-        <v>374</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="37" t="s">
-        <v>367</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="37" t="s">
-        <v>368</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="37" t="s">
-        <v>369</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="37" t="s">
-        <v>386</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="37" t="s">
-        <v>376</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="37" t="s">
-        <v>377</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="37" t="s">
-        <v>370</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="37" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="37"/>
-    </row>
-    <row r="30" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="1"/>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="6" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="24" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="24" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="25"/>
-    </row>
-    <row r="59" spans="1:1" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A59" s="26" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" ht="33" x14ac:dyDescent="0.3">
-      <c r="A60" s="26" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="24" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="24" t="s">
-        <v>391</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>